--- a/AAII_Financials/Yearly/GFS_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/GFS_YR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Yearly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Yearly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,12 +17,12 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="314" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="320" uniqueCount="92">
   <si>
     <t>GFS</t>
   </si>
@@ -656,50 +656,50 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:M102"/>
+  <dimension ref="A5:N102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="7" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="12" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="8" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="13" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E7" s="2">
         <v>44926</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>44561</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44196</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>43830</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>43465</v>
       </c>
-      <c r="I7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="J7" s="2" t="s">
         <v>3</v>
       </c>
@@ -709,30 +709,33 @@
       <c r="L7" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="M7" s="2"/>
-    </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="M7" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="N7" s="2"/>
+    </row>
+    <row r="8" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>7392000</v>
+      </c>
+      <c r="E8" s="3">
         <v>8108000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>6585100</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>4850500</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>5812800</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>6196000</v>
       </c>
-      <c r="I8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J8" s="3" t="s">
         <v>3</v>
       </c>
@@ -742,30 +745,33 @@
       <c r="L8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M8" s="3"/>
-    </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="M8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N8" s="3"/>
+    </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>5291000</v>
+      </c>
+      <c r="E9" s="3">
         <v>5869000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>5571800</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>5563200</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>6345000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>6646100</v>
       </c>
-      <c r="I9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J9" s="3" t="s">
         <v>3</v>
       </c>
@@ -775,30 +781,33 @@
       <c r="L9" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M9" s="3"/>
-    </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="M9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N9" s="3"/>
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>2101000</v>
+      </c>
+      <c r="E10" s="3">
         <v>2239000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>1013300</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>-712700</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>-532200</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>-450100</v>
       </c>
-      <c r="I10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J10" s="3" t="s">
         <v>3</v>
       </c>
@@ -808,9 +817,12 @@
       <c r="L10" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M10" s="3"/>
-    </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="M10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N10" s="3"/>
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -824,29 +836,30 @@
       <c r="K11" s="3"/>
       <c r="L11" s="3"/>
       <c r="M11" s="3"/>
-    </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N11" s="3"/>
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>428000</v>
+      </c>
+      <c r="E12" s="3">
         <v>372000</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>331000</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>255300</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>373600</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>662600</v>
       </c>
-      <c r="I12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J12" s="3" t="s">
         <v>3</v>
       </c>
@@ -856,9 +869,12 @@
       <c r="L12" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M12" s="3"/>
-    </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="M12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N12" s="3"/>
+    </row>
+    <row r="13" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -889,30 +905,33 @@
       <c r="L13" s="3">
         <v>0</v>
       </c>
-      <c r="M13" s="3"/>
-    </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="M13" s="3">
+        <v>0</v>
+      </c>
+      <c r="N13" s="3"/>
+    </row>
+    <row r="14" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>71000</v>
+      </c>
+      <c r="E14" s="3">
         <v>-309000</v>
       </c>
-      <c r="E14" s="3">
-        <v>0</v>
-      </c>
       <c r="F14" s="3">
+        <v>0</v>
+      </c>
+      <c r="G14" s="3">
         <v>-271500</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>-550600</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>694300</v>
       </c>
-      <c r="I14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J14" s="3" t="s">
         <v>3</v>
       </c>
@@ -922,30 +941,33 @@
       <c r="L14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M14" s="3"/>
-    </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="M14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N14" s="3"/>
+    </row>
+    <row r="15" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D15" s="3">
+      <c r="D15" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E15" s="3">
         <v>155000</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>197000</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>335600</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>296000</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>341600</v>
       </c>
-      <c r="I15" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J15" s="3" t="s">
         <v>3</v>
       </c>
@@ -955,9 +977,12 @@
       <c r="L15" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M15" s="3"/>
-    </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="M15" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N15" s="3"/>
+    </row>
+    <row r="16" spans="1:14" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -968,29 +993,30 @@
       <c r="K16" s="3"/>
       <c r="L16" s="3"/>
       <c r="M16" s="3"/>
-    </row>
-    <row r="17" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N16" s="3"/>
+    </row>
+    <row r="17" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>6263000</v>
+      </c>
+      <c r="E17" s="3">
         <v>6538000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>6644900</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>6212300</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>6823000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>8719300</v>
       </c>
-      <c r="I17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J17" s="3" t="s">
         <v>3</v>
       </c>
@@ -1000,30 +1026,33 @@
       <c r="L17" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M17" s="3"/>
-    </row>
-    <row r="18" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N17" s="3"/>
+    </row>
+    <row r="18" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>1129000</v>
+      </c>
+      <c r="E18" s="3">
         <v>1570000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-59800</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-1361800</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-1010200</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-2523300</v>
       </c>
-      <c r="I18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1033,9 +1062,12 @@
       <c r="L18" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M18" s="3"/>
-    </row>
-    <row r="19" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N18" s="3"/>
+    </row>
+    <row r="19" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1049,29 +1081,30 @@
       <c r="K19" s="3"/>
       <c r="L19" s="3"/>
       <c r="M19" s="3"/>
-    </row>
-    <row r="20" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N19" s="3"/>
+    </row>
+    <row r="20" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-45000</v>
+      </c>
+      <c r="E20" s="3">
         <v>67000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-4600</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>149700</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>89000</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>70800</v>
       </c>
-      <c r="I20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J20" s="3" t="s">
         <v>3</v>
       </c>
@@ -1081,30 +1114,33 @@
       <c r="L20" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M20" s="3"/>
-    </row>
-    <row r="21" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N20" s="3"/>
+    </row>
+    <row r="21" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>2535000</v>
+      </c>
+      <c r="E21" s="3">
         <v>3260000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>1554500</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>1310400</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>1757000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>495500</v>
       </c>
-      <c r="I21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1114,30 +1150,33 @@
       <c r="L21" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M21" s="3"/>
-    </row>
-    <row r="22" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N21" s="3"/>
+    </row>
+    <row r="22" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D22" s="3">
+      <c r="D22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E22" s="3">
         <v>105000</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>111300</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>151000</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>225900</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>157100</v>
       </c>
-      <c r="I22" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J22" s="3" t="s">
         <v>3</v>
       </c>
@@ -1147,30 +1186,33 @@
       <c r="L22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M22" s="3"/>
-    </row>
-    <row r="23" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N22" s="3"/>
+    </row>
+    <row r="23" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>1084000</v>
+      </c>
+      <c r="E23" s="3">
         <v>1532000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-175700</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-1363100</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-1147100</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-2609600</v>
       </c>
-      <c r="I23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J23" s="3" t="s">
         <v>3</v>
       </c>
@@ -1180,30 +1222,33 @@
       <c r="L23" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M23" s="3"/>
-    </row>
-    <row r="24" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N23" s="3"/>
+    </row>
+    <row r="24" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>66000</v>
+      </c>
+      <c r="E24" s="3">
         <v>86000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>78300</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>-12300</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>224100</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>16400</v>
       </c>
-      <c r="I24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J24" s="3" t="s">
         <v>3</v>
       </c>
@@ -1213,9 +1258,12 @@
       <c r="L24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M24" s="3"/>
-    </row>
-    <row r="25" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N24" s="3"/>
+    </row>
+    <row r="25" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1246,30 +1294,33 @@
       <c r="L25" s="3">
         <v>0</v>
       </c>
-      <c r="M25" s="3"/>
-    </row>
-    <row r="26" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M25" s="3">
+        <v>0</v>
+      </c>
+      <c r="N25" s="3"/>
+    </row>
+    <row r="26" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>1018000</v>
+      </c>
+      <c r="E26" s="3">
         <v>1446000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-253900</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-1350900</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-1371200</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-2626000</v>
       </c>
-      <c r="I26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J26" s="3" t="s">
         <v>3</v>
       </c>
@@ -1279,30 +1330,33 @@
       <c r="L26" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M26" s="3"/>
-    </row>
-    <row r="27" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N26" s="3"/>
+    </row>
+    <row r="27" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>1020000</v>
+      </c>
+      <c r="E27" s="3">
         <v>1448000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-250300</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-1347600</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-1371200</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-2553600</v>
       </c>
-      <c r="I27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J27" s="3" t="s">
         <v>3</v>
       </c>
@@ -1312,9 +1366,12 @@
       <c r="L27" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M27" s="3"/>
-    </row>
-    <row r="28" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N27" s="3"/>
+    </row>
+    <row r="28" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1345,9 +1402,12 @@
       <c r="L28" s="3">
         <v>0</v>
       </c>
-      <c r="M28" s="3"/>
-    </row>
-    <row r="29" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M28" s="3">
+        <v>0</v>
+      </c>
+      <c r="N28" s="3"/>
+    </row>
+    <row r="29" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1357,18 +1417,18 @@
       <c r="E29" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="F29" s="3">
-        <v>0</v>
+      <c r="F29" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="G29" s="3">
         <v>0</v>
       </c>
       <c r="H29" s="3">
+        <v>0</v>
+      </c>
+      <c r="I29" s="3">
         <v>-148000</v>
       </c>
-      <c r="I29" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J29" s="3" t="s">
         <v>3</v>
       </c>
@@ -1378,9 +1438,12 @@
       <c r="L29" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M29" s="3"/>
-    </row>
-    <row r="30" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M29" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N29" s="3"/>
+    </row>
+    <row r="30" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1411,9 +1474,12 @@
       <c r="L30" s="3">
         <v>0</v>
       </c>
-      <c r="M30" s="3"/>
-    </row>
-    <row r="31" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M30" s="3">
+        <v>0</v>
+      </c>
+      <c r="N30" s="3"/>
+    </row>
+    <row r="31" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1444,30 +1510,33 @@
       <c r="L31" s="3">
         <v>0</v>
       </c>
-      <c r="M31" s="3"/>
-    </row>
-    <row r="32" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M31" s="3">
+        <v>0</v>
+      </c>
+      <c r="N31" s="3"/>
+    </row>
+    <row r="32" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>45000</v>
+      </c>
+      <c r="E32" s="3">
         <v>-67000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>4600</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-149700</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-89000</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-70800</v>
       </c>
-      <c r="I32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J32" s="3" t="s">
         <v>3</v>
       </c>
@@ -1477,30 +1546,33 @@
       <c r="L32" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M32" s="3"/>
-    </row>
-    <row r="33" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N32" s="3"/>
+    </row>
+    <row r="33" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>1020000</v>
+      </c>
+      <c r="E33" s="3">
         <v>1448000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-250300</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-1347600</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-1371200</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-2701600</v>
       </c>
-      <c r="I33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J33" s="3" t="s">
         <v>3</v>
       </c>
@@ -1510,9 +1582,12 @@
       <c r="L33" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M33" s="3"/>
-    </row>
-    <row r="34" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N33" s="3"/>
+    </row>
+    <row r="34" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1543,30 +1618,33 @@
       <c r="L34" s="3">
         <v>0</v>
       </c>
-      <c r="M34" s="3"/>
-    </row>
-    <row r="35" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M34" s="3">
+        <v>0</v>
+      </c>
+      <c r="N34" s="3"/>
+    </row>
+    <row r="35" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>1020000</v>
+      </c>
+      <c r="E35" s="3">
         <v>1448000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-250300</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-1347600</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-1371200</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-2701600</v>
       </c>
-      <c r="I35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J35" s="3" t="s">
         <v>3</v>
       </c>
@@ -1576,35 +1654,38 @@
       <c r="L35" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M35" s="3"/>
-    </row>
-    <row r="37" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N35" s="3"/>
+    </row>
+    <row r="37" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E38" s="2">
         <v>44926</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>44561</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44196</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>43830</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>43465</v>
       </c>
-      <c r="I38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="J38" s="2" t="s">
         <v>3</v>
       </c>
@@ -1614,9 +1695,12 @@
       <c r="L38" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="M38" s="2"/>
-    </row>
-    <row r="39" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M38" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="N38" s="2"/>
+    </row>
+    <row r="39" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1630,8 +1714,9 @@
       <c r="K39" s="3"/>
       <c r="L39" s="3"/>
       <c r="M39" s="3"/>
-    </row>
-    <row r="40" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N39" s="3"/>
+    </row>
+    <row r="40" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1645,26 +1730,27 @@
       <c r="K40" s="3"/>
       <c r="L40" s="3"/>
       <c r="M40" s="3"/>
-    </row>
-    <row r="41" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N40" s="3"/>
+    </row>
+    <row r="41" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>2387000</v>
+      </c>
+      <c r="E41" s="3">
         <v>998000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>764200</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>347900</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>396700</v>
       </c>
-      <c r="H41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I41" s="3" t="s">
         <v>3</v>
       </c>
@@ -1677,27 +1763,30 @@
       <c r="L41" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M41" s="3"/>
-    </row>
-    <row r="42" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N41" s="3"/>
+    </row>
+    <row r="42" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>1033000</v>
+      </c>
+      <c r="E42" s="3">
         <v>2055000</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>2198200</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>610700</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>607400</v>
       </c>
-      <c r="H42" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I42" s="3" t="s">
         <v>3</v>
       </c>
@@ -1710,27 +1799,30 @@
       <c r="L42" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M42" s="3"/>
-    </row>
-    <row r="43" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M42" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N42" s="3"/>
+    </row>
+    <row r="43" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>1420000</v>
+      </c>
+      <c r="E43" s="3">
         <v>1408000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>1207700</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>1009500</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>2039300</v>
       </c>
-      <c r="H43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I43" s="3" t="s">
         <v>3</v>
       </c>
@@ -1743,27 +1835,30 @@
       <c r="L43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M43" s="3"/>
-    </row>
-    <row r="44" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N43" s="3"/>
+    </row>
+    <row r="44" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>1487000</v>
+      </c>
+      <c r="E44" s="3">
         <v>1339000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>1121300</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>919500</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>351900</v>
       </c>
-      <c r="H44" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I44" s="3" t="s">
         <v>3</v>
       </c>
@@ -1776,9 +1871,12 @@
       <c r="L44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M44" s="3"/>
-    </row>
-    <row r="45" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N44" s="3"/>
+    </row>
+    <row r="45" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -1788,15 +1886,15 @@
       <c r="E45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="F45" s="3">
+      <c r="F45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G45" s="3">
         <v>99100</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>118800</v>
       </c>
-      <c r="H45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I45" s="3" t="s">
         <v>3</v>
       </c>
@@ -1809,27 +1907,30 @@
       <c r="L45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M45" s="3"/>
-    </row>
-    <row r="46" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N45" s="3"/>
+    </row>
+    <row r="46" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>6327000</v>
+      </c>
+      <c r="E46" s="3">
         <v>5800000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>5291300</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>2986700</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>3514200</v>
       </c>
-      <c r="H46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I46" s="3" t="s">
         <v>3</v>
       </c>
@@ -1842,27 +1943,30 @@
       <c r="L46" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M46" s="3"/>
-    </row>
-    <row r="47" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N46" s="3"/>
+    </row>
+    <row r="47" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>468000</v>
+      </c>
+      <c r="E47" s="3">
         <v>519000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>53200</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>115500</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>271000</v>
       </c>
-      <c r="H47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I47" s="3" t="s">
         <v>3</v>
       </c>
@@ -1875,27 +1979,30 @@
       <c r="L47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M47" s="3"/>
-    </row>
-    <row r="48" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N47" s="3"/>
+    </row>
+    <row r="48" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>10164000</v>
+      </c>
+      <c r="E48" s="3">
         <v>10596000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>8713000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>8226200</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>9611300</v>
       </c>
-      <c r="H48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I48" s="3" t="s">
         <v>3</v>
       </c>
@@ -1908,27 +2015,30 @@
       <c r="L48" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M48" s="3"/>
-    </row>
-    <row r="49" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N48" s="3"/>
+    </row>
+    <row r="49" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="D49" s="3">
+      <c r="D49" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E49" s="3">
         <v>363000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>376700</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>547900</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>634800</v>
       </c>
-      <c r="H49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I49" s="3" t="s">
         <v>3</v>
       </c>
@@ -1941,9 +2051,12 @@
       <c r="L49" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M49" s="3"/>
-    </row>
-    <row r="50" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M49" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N49" s="3"/>
+    </row>
+    <row r="50" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -1974,9 +2087,12 @@
       <c r="L50" s="3">
         <v>0</v>
       </c>
-      <c r="M50" s="3"/>
-    </row>
-    <row r="51" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M50" s="3">
+        <v>0</v>
+      </c>
+      <c r="N50" s="3"/>
+    </row>
+    <row r="51" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2007,27 +2123,30 @@
       <c r="L51" s="3">
         <v>0</v>
       </c>
-      <c r="M51" s="3"/>
-    </row>
-    <row r="52" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M51" s="3">
+        <v>0</v>
+      </c>
+      <c r="N51" s="3"/>
+    </row>
+    <row r="52" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>1085000</v>
+      </c>
+      <c r="E52" s="3">
         <v>563000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>593400</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>445200</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>466300</v>
       </c>
-      <c r="H52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I52" s="3" t="s">
         <v>3</v>
       </c>
@@ -2040,9 +2159,12 @@
       <c r="L52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M52" s="3"/>
-    </row>
-    <row r="53" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N52" s="3"/>
+    </row>
+    <row r="53" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2073,27 +2195,30 @@
       <c r="L53" s="3">
         <v>0</v>
       </c>
-      <c r="M53" s="3"/>
-    </row>
-    <row r="54" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M53" s="3">
+        <v>0</v>
+      </c>
+      <c r="N53" s="3"/>
+    </row>
+    <row r="54" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>18044000</v>
+      </c>
+      <c r="E54" s="3">
         <v>17841000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>15027600</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>12321600</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>14497500</v>
       </c>
-      <c r="H54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I54" s="3" t="s">
         <v>3</v>
       </c>
@@ -2106,9 +2231,12 @@
       <c r="L54" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M54" s="3"/>
-    </row>
-    <row r="55" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N54" s="3"/>
+    </row>
+    <row r="55" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2122,8 +2250,9 @@
       <c r="K55" s="3"/>
       <c r="L55" s="3"/>
       <c r="M55" s="3"/>
-    </row>
-    <row r="56" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N55" s="3"/>
+    </row>
+    <row r="56" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2137,26 +2266,27 @@
       <c r="K56" s="3"/>
       <c r="L56" s="3"/>
       <c r="M56" s="3"/>
-    </row>
-    <row r="57" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N56" s="3"/>
+    </row>
+    <row r="57" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="D57" s="3">
+      <c r="D57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E57" s="3">
         <v>532000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>551100</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>600500</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>559000</v>
       </c>
-      <c r="H57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I57" s="3" t="s">
         <v>3</v>
       </c>
@@ -2169,27 +2299,30 @@
       <c r="L57" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M57" s="3"/>
-    </row>
-    <row r="58" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N57" s="3"/>
+    </row>
+    <row r="58" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>571000</v>
+      </c>
+      <c r="E58" s="3">
         <v>298000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>432200</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>513100</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>817800</v>
       </c>
-      <c r="H58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I58" s="3" t="s">
         <v>3</v>
       </c>
@@ -2202,27 +2335,30 @@
       <c r="L58" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M58" s="3"/>
-    </row>
-    <row r="59" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N58" s="3"/>
+    </row>
+    <row r="59" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>2528000</v>
+      </c>
+      <c r="E59" s="3">
         <v>2529000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>2179500</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>782500</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>959300</v>
       </c>
-      <c r="H59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I59" s="3" t="s">
         <v>3</v>
       </c>
@@ -2235,27 +2371,30 @@
       <c r="L59" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M59" s="3"/>
-    </row>
-    <row r="60" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N59" s="3"/>
+    </row>
+    <row r="60" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>3099000</v>
+      </c>
+      <c r="E60" s="3">
         <v>3359000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>3162900</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>1896100</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>2336100</v>
       </c>
-      <c r="H60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I60" s="3" t="s">
         <v>3</v>
       </c>
@@ -2268,27 +2407,30 @@
       <c r="L60" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M60" s="3"/>
-    </row>
-    <row r="61" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N60" s="3"/>
+    </row>
+    <row r="61" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>1801000</v>
+      </c>
+      <c r="E61" s="3">
         <v>2558000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>2006400</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>2289400</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>2430500</v>
       </c>
-      <c r="H61" s="3">
-        <v>0</v>
-      </c>
       <c r="I61" s="3">
         <v>0</v>
       </c>
@@ -2301,27 +2443,30 @@
       <c r="L61" s="3">
         <v>0</v>
       </c>
-      <c r="M61" s="3"/>
-    </row>
-    <row r="62" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M61" s="3">
+        <v>0</v>
+      </c>
+      <c r="N61" s="3"/>
+    </row>
+    <row r="62" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>1993000</v>
+      </c>
+      <c r="E62" s="3">
         <v>1964000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>1825200</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>894700</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>711800</v>
       </c>
-      <c r="H62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I62" s="3" t="s">
         <v>3</v>
       </c>
@@ -2334,9 +2479,12 @@
       <c r="L62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M62" s="3"/>
-    </row>
-    <row r="63" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N62" s="3"/>
+    </row>
+    <row r="63" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2367,9 +2515,12 @@
       <c r="L63" s="3">
         <v>0</v>
       </c>
-      <c r="M63" s="3"/>
-    </row>
-    <row r="64" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M63" s="3">
+        <v>0</v>
+      </c>
+      <c r="N63" s="3"/>
+    </row>
+    <row r="64" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2400,9 +2551,12 @@
       <c r="L64" s="3">
         <v>0</v>
       </c>
-      <c r="M64" s="3"/>
-    </row>
-    <row r="65" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M64" s="3">
+        <v>0</v>
+      </c>
+      <c r="N64" s="3"/>
+    </row>
+    <row r="65" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2433,27 +2587,30 @@
       <c r="L65" s="3">
         <v>0</v>
       </c>
-      <c r="M65" s="3"/>
-    </row>
-    <row r="66" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M65" s="3">
+        <v>0</v>
+      </c>
+      <c r="N65" s="3"/>
+    </row>
+    <row r="66" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>6940000</v>
+      </c>
+      <c r="E66" s="3">
         <v>7928000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>7052100</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>5145300</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>5478400</v>
       </c>
-      <c r="H66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I66" s="3" t="s">
         <v>3</v>
       </c>
@@ -2466,9 +2623,12 @@
       <c r="L66" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M66" s="3"/>
-    </row>
-    <row r="67" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N66" s="3"/>
+    </row>
+    <row r="67" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2482,8 +2642,9 @@
       <c r="K67" s="3"/>
       <c r="L67" s="3"/>
       <c r="M67" s="3"/>
-    </row>
-    <row r="68" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N67" s="3"/>
+    </row>
+    <row r="68" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2514,9 +2675,12 @@
       <c r="L68" s="3">
         <v>0</v>
       </c>
-      <c r="M68" s="3"/>
-    </row>
-    <row r="69" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M68" s="3">
+        <v>0</v>
+      </c>
+      <c r="N68" s="3"/>
+    </row>
+    <row r="69" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2547,9 +2711,12 @@
       <c r="L69" s="3">
         <v>0</v>
       </c>
-      <c r="M69" s="3"/>
-    </row>
-    <row r="70" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M69" s="3">
+        <v>0</v>
+      </c>
+      <c r="N69" s="3"/>
+    </row>
+    <row r="70" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -2580,9 +2747,12 @@
       <c r="L70" s="3">
         <v>0</v>
       </c>
-      <c r="M70" s="3"/>
-    </row>
-    <row r="71" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M70" s="3">
+        <v>0</v>
+      </c>
+      <c r="N70" s="3"/>
+    </row>
+    <row r="71" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -2613,27 +2783,30 @@
       <c r="L71" s="3">
         <v>0</v>
       </c>
-      <c r="M71" s="3"/>
-    </row>
-    <row r="72" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M71" s="3">
+        <v>0</v>
+      </c>
+      <c r="N71" s="3"/>
+    </row>
+    <row r="72" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-13001000</v>
+      </c>
+      <c r="E72" s="3">
         <v>-14021000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-15468800</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-15218500</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-13870900</v>
       </c>
-      <c r="H72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I72" s="3" t="s">
         <v>3</v>
       </c>
@@ -2646,9 +2819,12 @@
       <c r="L72" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M72" s="3"/>
-    </row>
-    <row r="73" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N72" s="3"/>
+    </row>
+    <row r="73" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -2679,9 +2855,12 @@
       <c r="L73" s="3">
         <v>0</v>
       </c>
-      <c r="M73" s="3"/>
-    </row>
-    <row r="74" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M73" s="3">
+        <v>0</v>
+      </c>
+      <c r="N73" s="3"/>
+    </row>
+    <row r="74" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -2712,9 +2891,12 @@
       <c r="L74" s="3">
         <v>0</v>
       </c>
-      <c r="M74" s="3"/>
-    </row>
-    <row r="75" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M74" s="3">
+        <v>0</v>
+      </c>
+      <c r="N74" s="3"/>
+    </row>
+    <row r="75" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -2745,27 +2927,30 @@
       <c r="L75" s="3">
         <v>0</v>
       </c>
-      <c r="M75" s="3"/>
-    </row>
-    <row r="76" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M75" s="3">
+        <v>0</v>
+      </c>
+      <c r="N75" s="3"/>
+    </row>
+    <row r="76" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>11104000</v>
+      </c>
+      <c r="E76" s="3">
         <v>9913000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>7975500</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>7176400</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>9019100</v>
       </c>
-      <c r="H76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I76" s="3" t="s">
         <v>3</v>
       </c>
@@ -2778,9 +2963,12 @@
       <c r="L76" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M76" s="3"/>
-    </row>
-    <row r="77" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N76" s="3"/>
+    </row>
+    <row r="77" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -2811,35 +2999,38 @@
       <c r="L77" s="3">
         <v>0</v>
       </c>
-      <c r="M77" s="3"/>
-    </row>
-    <row r="79" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M77" s="3">
+        <v>0</v>
+      </c>
+      <c r="N77" s="3"/>
+    </row>
+    <row r="79" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E80" s="2">
         <v>44926</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>44561</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44196</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>43830</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>43465</v>
       </c>
-      <c r="I80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="J80" s="2" t="s">
         <v>3</v>
       </c>
@@ -2849,30 +3040,33 @@
       <c r="L80" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="M80" s="2"/>
-    </row>
-    <row r="81" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M80" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="N80" s="2"/>
+    </row>
+    <row r="81" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>1020000</v>
+      </c>
+      <c r="E81" s="3">
         <v>1448000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-250300</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-1347600</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-1371200</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-2701600</v>
       </c>
-      <c r="I81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J81" s="3" t="s">
         <v>3</v>
       </c>
@@ -2882,9 +3076,12 @@
       <c r="L81" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M81" s="3"/>
-    </row>
-    <row r="82" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N81" s="3"/>
+    </row>
+    <row r="82" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -2898,29 +3095,30 @@
       <c r="K82" s="3"/>
       <c r="L82" s="3"/>
       <c r="M82" s="3"/>
-    </row>
-    <row r="83" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N82" s="3"/>
+    </row>
+    <row r="83" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>1451000</v>
+      </c>
+      <c r="E83" s="3">
         <v>1623000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>1618800</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>2522500</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>2678200</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>2947900</v>
       </c>
-      <c r="I83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J83" s="3" t="s">
         <v>3</v>
       </c>
@@ -2930,9 +3128,12 @@
       <c r="L83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M83" s="3"/>
-    </row>
-    <row r="84" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N83" s="3"/>
+    </row>
+    <row r="84" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -2963,9 +3164,12 @@
       <c r="L84" s="3">
         <v>0</v>
       </c>
-      <c r="M84" s="3"/>
-    </row>
-    <row r="85" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M84" s="3">
+        <v>0</v>
+      </c>
+      <c r="N84" s="3"/>
+    </row>
+    <row r="85" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -2996,9 +3200,12 @@
       <c r="L85" s="3">
         <v>0</v>
       </c>
-      <c r="M85" s="3"/>
-    </row>
-    <row r="86" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M85" s="3">
+        <v>0</v>
+      </c>
+      <c r="N85" s="3"/>
+    </row>
+    <row r="86" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3029,9 +3236,12 @@
       <c r="L86" s="3">
         <v>0</v>
       </c>
-      <c r="M86" s="3"/>
-    </row>
-    <row r="87" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M86" s="3">
+        <v>0</v>
+      </c>
+      <c r="N86" s="3"/>
+    </row>
+    <row r="87" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3062,9 +3272,12 @@
       <c r="L87" s="3">
         <v>0</v>
       </c>
-      <c r="M87" s="3"/>
-    </row>
-    <row r="88" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M87" s="3">
+        <v>0</v>
+      </c>
+      <c r="N87" s="3"/>
+    </row>
+    <row r="88" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3095,30 +3308,33 @@
       <c r="L88" s="3">
         <v>0</v>
       </c>
-      <c r="M88" s="3"/>
-    </row>
-    <row r="89" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M88" s="3">
+        <v>0</v>
+      </c>
+      <c r="N88" s="3"/>
+    </row>
+    <row r="89" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>2125000</v>
+      </c>
+      <c r="E89" s="3">
         <v>2624000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>2839000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>1005900</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>496800</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>279300</v>
       </c>
-      <c r="I89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J89" s="3" t="s">
         <v>3</v>
       </c>
@@ -3128,9 +3344,12 @@
       <c r="L89" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M89" s="3"/>
-    </row>
-    <row r="90" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N89" s="3"/>
+    </row>
+    <row r="90" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3144,29 +3363,30 @@
       <c r="K90" s="3"/>
       <c r="L90" s="3"/>
       <c r="M90" s="3"/>
-    </row>
-    <row r="91" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N90" s="3"/>
+    </row>
+    <row r="91" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-1804000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-3059000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-1661600</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-449300</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-587900</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-1150300</v>
       </c>
-      <c r="I91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J91" s="3" t="s">
         <v>3</v>
       </c>
@@ -3176,9 +3396,12 @@
       <c r="L91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M91" s="3"/>
-    </row>
-    <row r="92" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N91" s="3"/>
+    </row>
+    <row r="92" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3209,9 +3432,12 @@
       <c r="L92" s="3">
         <v>0</v>
       </c>
-      <c r="M92" s="3"/>
-    </row>
-    <row r="93" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M92" s="3">
+        <v>0</v>
+      </c>
+      <c r="N92" s="3"/>
+    </row>
+    <row r="93" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3242,30 +3468,33 @@
       <c r="L93" s="3">
         <v>0</v>
       </c>
-      <c r="M93" s="3"/>
-    </row>
-    <row r="94" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M93" s="3">
+        <v>0</v>
+      </c>
+      <c r="N93" s="3"/>
+    </row>
+    <row r="94" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-1882000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-4058000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-1450300</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-366200</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>343700</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-1167200</v>
       </c>
-      <c r="I94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J94" s="3" t="s">
         <v>3</v>
       </c>
@@ -3275,9 +3504,12 @@
       <c r="L94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M94" s="3"/>
-    </row>
-    <row r="95" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N94" s="3"/>
+    </row>
+    <row r="95" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3291,8 +3523,9 @@
       <c r="K95" s="3"/>
       <c r="L95" s="3"/>
       <c r="M95" s="3"/>
-    </row>
-    <row r="96" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N95" s="3"/>
+    </row>
+    <row r="96" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -3323,9 +3556,12 @@
       <c r="L96" s="3">
         <v>0</v>
       </c>
-      <c r="M96" s="3"/>
-    </row>
-    <row r="97" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M96" s="3">
+        <v>0</v>
+      </c>
+      <c r="N96" s="3"/>
+    </row>
+    <row r="97" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3356,9 +3592,12 @@
       <c r="L97" s="3">
         <v>0</v>
       </c>
-      <c r="M97" s="3"/>
-    </row>
-    <row r="98" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M97" s="3">
+        <v>0</v>
+      </c>
+      <c r="N97" s="3"/>
+    </row>
+    <row r="98" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -3389,9 +3628,12 @@
       <c r="L98" s="3">
         <v>0</v>
       </c>
-      <c r="M98" s="3"/>
-    </row>
-    <row r="99" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M98" s="3">
+        <v>0</v>
+      </c>
+      <c r="N98" s="3"/>
+    </row>
+    <row r="99" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -3422,30 +3664,33 @@
       <c r="L99" s="3">
         <v>0</v>
       </c>
-      <c r="M99" s="3"/>
-    </row>
-    <row r="100" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M99" s="3">
+        <v>0</v>
+      </c>
+      <c r="N99" s="3"/>
+    </row>
+    <row r="100" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-212000</v>
+      </c>
+      <c r="E100" s="3">
         <v>842000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>650400</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-732700</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-683800</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>1132100</v>
       </c>
-      <c r="I100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J100" s="3" t="s">
         <v>3</v>
       </c>
@@ -3455,30 +3700,33 @@
       <c r="L100" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M100" s="3"/>
-    </row>
-    <row r="101" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N100" s="3"/>
+    </row>
+    <row r="101" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>4000</v>
+      </c>
+      <c r="E101" s="3">
         <v>5000</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-8100</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>3800</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-3400</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-1300</v>
       </c>
-      <c r="I101" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J101" s="3" t="s">
         <v>3</v>
       </c>
@@ -3488,30 +3736,33 @@
       <c r="L101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M101" s="3"/>
-    </row>
-    <row r="102" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N101" s="3"/>
+    </row>
+    <row r="102" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>35000</v>
+      </c>
+      <c r="E102" s="3">
         <v>-587000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>2031100</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-89200</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>153300</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>242900</v>
       </c>
-      <c r="I102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J102" s="3" t="s">
         <v>3</v>
       </c>
@@ -3521,7 +3772,10 @@
       <c r="L102" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M102" s="3"/>
+      <c r="M102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/AAII_Financials/Yearly/GFS_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/GFS_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="320" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="316" uniqueCount="92">
   <si>
     <t>GFS</t>
   </si>
@@ -755,10 +755,10 @@
         <v>5</v>
       </c>
       <c r="D9" s="3">
-        <v>5291000</v>
+        <v>5320000</v>
       </c>
       <c r="E9" s="3">
-        <v>5869000</v>
+        <v>5899000</v>
       </c>
       <c r="F9" s="3">
         <v>5571800</v>
@@ -791,10 +791,10 @@
         <v>6</v>
       </c>
       <c r="D10" s="3">
-        <v>2101000</v>
+        <v>2072000</v>
       </c>
       <c r="E10" s="3">
-        <v>2239000</v>
+        <v>2209000</v>
       </c>
       <c r="F10" s="3">
         <v>1013300</v>
@@ -843,10 +843,10 @@
         <v>8</v>
       </c>
       <c r="D12" s="3">
-        <v>428000</v>
+        <v>356000</v>
       </c>
       <c r="E12" s="3">
-        <v>372000</v>
+        <v>383000</v>
       </c>
       <c r="F12" s="3">
         <v>331000</v>
@@ -950,8 +950,8 @@
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D15" s="3" t="s">
-        <v>3</v>
+      <c r="D15" s="3">
+        <v>131000</v>
       </c>
       <c r="E15" s="3">
         <v>155000</v>
@@ -1088,7 +1088,7 @@
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>-45000</v>
+        <v>69000</v>
       </c>
       <c r="E20" s="3">
         <v>67000</v>
@@ -1124,7 +1124,7 @@
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>2535000</v>
+        <v>2649000</v>
       </c>
       <c r="E21" s="3">
         <v>3260000</v>
@@ -1159,8 +1159,8 @@
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D22" s="3" t="s">
-        <v>3</v>
+      <c r="D22" s="3">
+        <v>114000</v>
       </c>
       <c r="E22" s="3">
         <v>105000</v>
@@ -1520,7 +1520,7 @@
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>45000</v>
+        <v>-69000</v>
       </c>
       <c r="E32" s="3">
         <v>-67000</v>
@@ -1773,7 +1773,7 @@
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>1033000</v>
+        <v>1085000</v>
       </c>
       <c r="E42" s="3">
         <v>2055000</v>
@@ -1809,7 +1809,7 @@
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>1420000</v>
+        <v>1368000</v>
       </c>
       <c r="E43" s="3">
         <v>1408000</v>
@@ -1953,7 +1953,7 @@
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>468000</v>
+        <v>684000</v>
       </c>
       <c r="E47" s="3">
         <v>519000</v>
@@ -2024,8 +2024,8 @@
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="D49" s="3" t="s">
-        <v>3</v>
+      <c r="D49" s="3">
+        <v>391000</v>
       </c>
       <c r="E49" s="3">
         <v>363000</v>
@@ -2133,7 +2133,7 @@
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>1085000</v>
+        <v>478000</v>
       </c>
       <c r="E52" s="3">
         <v>563000</v>
@@ -2272,8 +2272,8 @@
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="D57" s="3" t="s">
-        <v>3</v>
+      <c r="D57" s="3">
+        <v>511000</v>
       </c>
       <c r="E57" s="3">
         <v>532000</v>
@@ -2309,7 +2309,7 @@
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>571000</v>
+        <v>603000</v>
       </c>
       <c r="E58" s="3">
         <v>298000</v>
@@ -2345,7 +2345,7 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>2528000</v>
+        <v>1985000</v>
       </c>
       <c r="E59" s="3">
         <v>2529000</v>
@@ -2417,7 +2417,7 @@
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>1801000</v>
+        <v>2151000</v>
       </c>
       <c r="E61" s="3">
         <v>2558000</v>
@@ -2453,7 +2453,7 @@
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>1993000</v>
+        <v>1643000</v>
       </c>
       <c r="E62" s="3">
         <v>1964000</v>

--- a/AAII_Financials/Yearly/GFS_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/GFS_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="316" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="303" uniqueCount="92">
   <si>
     <t>GFS</t>
   </si>
@@ -725,10 +725,10 @@
         <v>8108000</v>
       </c>
       <c r="F8" s="3">
-        <v>6585100</v>
+        <v>6585000</v>
       </c>
       <c r="G8" s="3">
-        <v>4850500</v>
+        <v>4851000</v>
       </c>
       <c r="H8" s="3">
         <v>5812800</v>
@@ -755,16 +755,16 @@
         <v>5</v>
       </c>
       <c r="D9" s="3">
-        <v>5320000</v>
+        <v>5291000</v>
       </c>
       <c r="E9" s="3">
-        <v>5899000</v>
+        <v>5869000</v>
       </c>
       <c r="F9" s="3">
-        <v>5571800</v>
+        <v>5572000</v>
       </c>
       <c r="G9" s="3">
-        <v>5563200</v>
+        <v>5563000</v>
       </c>
       <c r="H9" s="3">
         <v>6345000</v>
@@ -791,16 +791,16 @@
         <v>6</v>
       </c>
       <c r="D10" s="3">
-        <v>2072000</v>
+        <v>2101000</v>
       </c>
       <c r="E10" s="3">
-        <v>2209000</v>
+        <v>2239000</v>
       </c>
       <c r="F10" s="3">
-        <v>1013300</v>
+        <v>1013000</v>
       </c>
       <c r="G10" s="3">
-        <v>-712700</v>
+        <v>-712000</v>
       </c>
       <c r="H10" s="3">
         <v>-532200</v>
@@ -843,22 +843,22 @@
         <v>8</v>
       </c>
       <c r="D12" s="3">
-        <v>356000</v>
+        <v>428000</v>
       </c>
       <c r="E12" s="3">
-        <v>383000</v>
+        <v>482000</v>
       </c>
       <c r="F12" s="3">
-        <v>331000</v>
+        <v>478000</v>
       </c>
       <c r="G12" s="3">
-        <v>255300</v>
+        <v>476000</v>
       </c>
       <c r="H12" s="3">
-        <v>373600</v>
+        <v>583000</v>
       </c>
       <c r="I12" s="3">
-        <v>662600</v>
+        <v>926200</v>
       </c>
       <c r="J12" s="3" t="s">
         <v>3</v>
@@ -915,22 +915,22 @@
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>71000</v>
+        <v>84000</v>
       </c>
       <c r="E14" s="3">
-        <v>-309000</v>
+        <v>-412000</v>
       </c>
       <c r="F14" s="3">
-        <v>0</v>
+        <v>-39000</v>
       </c>
       <c r="G14" s="3">
-        <v>-271500</v>
+        <v>-449000</v>
       </c>
       <c r="H14" s="3">
-        <v>-550600</v>
+        <v>-624700</v>
       </c>
       <c r="I14" s="3">
-        <v>694300</v>
+        <v>632900</v>
       </c>
       <c r="J14" s="3" t="s">
         <v>3</v>
@@ -951,25 +951,25 @@
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>131000</v>
+        <v>1387000</v>
       </c>
       <c r="E15" s="3">
-        <v>155000</v>
+        <v>1531000</v>
       </c>
       <c r="F15" s="3">
-        <v>197000</v>
+        <v>1537000</v>
       </c>
       <c r="G15" s="3">
-        <v>335600</v>
+        <v>2522000</v>
       </c>
       <c r="H15" s="3">
-        <v>296000</v>
+        <v>2678200</v>
       </c>
       <c r="I15" s="3">
-        <v>341600</v>
-      </c>
-      <c r="J15" s="3" t="s">
-        <v>3</v>
+        <v>2947900</v>
+      </c>
+      <c r="J15" s="3">
+        <v>0</v>
       </c>
       <c r="K15" s="3" t="s">
         <v>3</v>
@@ -1000,22 +1000,22 @@
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>6263000</v>
+        <v>6192000</v>
       </c>
       <c r="E17" s="3">
-        <v>6538000</v>
+        <v>6847000</v>
       </c>
       <c r="F17" s="3">
-        <v>6644900</v>
+        <v>6645000</v>
       </c>
       <c r="G17" s="3">
-        <v>6212300</v>
+        <v>6484000</v>
       </c>
       <c r="H17" s="3">
-        <v>6823000</v>
+        <v>7373600</v>
       </c>
       <c r="I17" s="3">
-        <v>8719300</v>
+        <v>8025100</v>
       </c>
       <c r="J17" s="3" t="s">
         <v>3</v>
@@ -1036,22 +1036,22 @@
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>1129000</v>
+        <v>1200000</v>
       </c>
       <c r="E18" s="3">
-        <v>1570000</v>
+        <v>1261000</v>
       </c>
       <c r="F18" s="3">
-        <v>-59800</v>
+        <v>-60000</v>
       </c>
       <c r="G18" s="3">
-        <v>-1361800</v>
+        <v>-1633000</v>
       </c>
       <c r="H18" s="3">
-        <v>-1010200</v>
+        <v>-1560800</v>
       </c>
       <c r="I18" s="3">
-        <v>-2523300</v>
+        <v>-1829000</v>
       </c>
       <c r="J18" s="3" t="s">
         <v>3</v>
@@ -1088,22 +1088,22 @@
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>69000</v>
+        <v>53000</v>
       </c>
       <c r="E20" s="3">
-        <v>67000</v>
+        <v>88000</v>
       </c>
       <c r="F20" s="3">
-        <v>-4600</v>
+        <v>57000</v>
       </c>
       <c r="G20" s="3">
-        <v>149700</v>
+        <v>51000</v>
       </c>
       <c r="H20" s="3">
-        <v>89000</v>
+        <v>19500</v>
       </c>
       <c r="I20" s="3">
-        <v>70800</v>
+        <v>20400</v>
       </c>
       <c r="J20" s="3" t="s">
         <v>3</v>
@@ -1124,25 +1124,25 @@
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>2649000</v>
+        <v>2534000</v>
       </c>
       <c r="E21" s="3">
-        <v>3260000</v>
+        <v>2704000</v>
       </c>
       <c r="F21" s="3">
-        <v>1554500</v>
+        <v>1420000</v>
       </c>
       <c r="G21" s="3">
-        <v>1310400</v>
+        <v>838000</v>
       </c>
       <c r="H21" s="3">
-        <v>1757000</v>
+        <v>1097800</v>
       </c>
       <c r="I21" s="3">
-        <v>495500</v>
-      </c>
-      <c r="J21" s="3" t="s">
-        <v>3</v>
+        <v>1098500</v>
+      </c>
+      <c r="J21" s="3">
+        <v>0</v>
       </c>
       <c r="K21" s="3" t="s">
         <v>3</v>
@@ -1160,22 +1160,22 @@
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>114000</v>
+        <v>101000</v>
       </c>
       <c r="E22" s="3">
-        <v>105000</v>
+        <v>92000</v>
       </c>
       <c r="F22" s="3">
-        <v>111300</v>
+        <v>99000</v>
       </c>
       <c r="G22" s="3">
-        <v>151000</v>
+        <v>133000</v>
       </c>
       <c r="H22" s="3">
-        <v>225900</v>
+        <v>202800</v>
       </c>
       <c r="I22" s="3">
-        <v>157100</v>
+        <v>137500</v>
       </c>
       <c r="J22" s="3" t="s">
         <v>3</v>
@@ -1202,10 +1202,10 @@
         <v>1532000</v>
       </c>
       <c r="F23" s="3">
-        <v>-175700</v>
+        <v>-176000</v>
       </c>
       <c r="G23" s="3">
-        <v>-1363100</v>
+        <v>-1365000</v>
       </c>
       <c r="H23" s="3">
         <v>-1147100</v>
@@ -1238,10 +1238,10 @@
         <v>86000</v>
       </c>
       <c r="F24" s="3">
-        <v>78300</v>
+        <v>78000</v>
       </c>
       <c r="G24" s="3">
-        <v>-12300</v>
+        <v>-12000</v>
       </c>
       <c r="H24" s="3">
         <v>224100</v>
@@ -1310,10 +1310,10 @@
         <v>1446000</v>
       </c>
       <c r="F26" s="3">
-        <v>-253900</v>
+        <v>-254000</v>
       </c>
       <c r="G26" s="3">
-        <v>-1350900</v>
+        <v>-1353000</v>
       </c>
       <c r="H26" s="3">
         <v>-1371200</v>
@@ -1346,16 +1346,16 @@
         <v>1448000</v>
       </c>
       <c r="F27" s="3">
-        <v>-250300</v>
+        <v>-250000</v>
       </c>
       <c r="G27" s="3">
-        <v>-1347600</v>
+        <v>-1350000</v>
       </c>
       <c r="H27" s="3">
         <v>-1371200</v>
       </c>
       <c r="I27" s="3">
-        <v>-2553600</v>
+        <v>-2701600</v>
       </c>
       <c r="J27" s="3" t="s">
         <v>3</v>
@@ -1411,14 +1411,14 @@
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="D29" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E29" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F29" s="3" t="s">
-        <v>3</v>
+      <c r="D29" s="3">
+        <v>0</v>
+      </c>
+      <c r="E29" s="3">
+        <v>0</v>
+      </c>
+      <c r="F29" s="3">
+        <v>0</v>
       </c>
       <c r="G29" s="3">
         <v>0</v>
@@ -1429,8 +1429,8 @@
       <c r="I29" s="3">
         <v>-148000</v>
       </c>
-      <c r="J29" s="3" t="s">
-        <v>3</v>
+      <c r="J29" s="3">
+        <v>0</v>
       </c>
       <c r="K29" s="3" t="s">
         <v>3</v>
@@ -1520,22 +1520,22 @@
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-69000</v>
+        <v>-53000</v>
       </c>
       <c r="E32" s="3">
-        <v>-67000</v>
+        <v>-88000</v>
       </c>
       <c r="F32" s="3">
-        <v>4600</v>
+        <v>-57000</v>
       </c>
       <c r="G32" s="3">
-        <v>-149700</v>
+        <v>-51000</v>
       </c>
       <c r="H32" s="3">
-        <v>-89000</v>
+        <v>-19500</v>
       </c>
       <c r="I32" s="3">
-        <v>-70800</v>
+        <v>-20400</v>
       </c>
       <c r="J32" s="3" t="s">
         <v>3</v>
@@ -1562,10 +1562,10 @@
         <v>1448000</v>
       </c>
       <c r="F33" s="3">
-        <v>-250300</v>
+        <v>-250000</v>
       </c>
       <c r="G33" s="3">
-        <v>-1347600</v>
+        <v>-1350000</v>
       </c>
       <c r="H33" s="3">
         <v>-1371200</v>
@@ -1634,10 +1634,10 @@
         <v>1448000</v>
       </c>
       <c r="F35" s="3">
-        <v>-250300</v>
+        <v>-250000</v>
       </c>
       <c r="G35" s="3">
-        <v>-1347600</v>
+        <v>-1350000</v>
       </c>
       <c r="H35" s="3">
         <v>-1371200</v>
@@ -1740,16 +1740,16 @@
         <v>2387000</v>
       </c>
       <c r="E41" s="3">
-        <v>998000</v>
+        <v>2352000</v>
       </c>
       <c r="F41" s="3">
-        <v>764200</v>
+        <v>2939000</v>
       </c>
       <c r="G41" s="3">
-        <v>347900</v>
+        <v>908100</v>
       </c>
       <c r="H41" s="3">
-        <v>396700</v>
+        <v>997300</v>
       </c>
       <c r="I41" s="3" t="s">
         <v>3</v>
@@ -1773,25 +1773,25 @@
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>1085000</v>
+        <v>1055000</v>
       </c>
       <c r="E42" s="3">
-        <v>2055000</v>
+        <v>622000</v>
       </c>
       <c r="F42" s="3">
-        <v>2198200</v>
+        <v>0</v>
       </c>
       <c r="G42" s="3">
-        <v>610700</v>
+        <v>0</v>
       </c>
       <c r="H42" s="3">
-        <v>607400</v>
-      </c>
-      <c r="I42" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J42" s="3" t="s">
-        <v>3</v>
+        <v>0</v>
+      </c>
+      <c r="I42" s="3">
+        <v>0</v>
+      </c>
+      <c r="J42" s="3">
+        <v>0</v>
       </c>
       <c r="K42" s="3" t="s">
         <v>3</v>
@@ -1815,13 +1815,13 @@
         <v>1408000</v>
       </c>
       <c r="F43" s="3">
-        <v>1207700</v>
+        <v>1208000</v>
       </c>
       <c r="G43" s="3">
-        <v>1009500</v>
+        <v>1108600</v>
       </c>
       <c r="H43" s="3">
-        <v>2039300</v>
+        <v>2065400</v>
       </c>
       <c r="I43" s="3" t="s">
         <v>3</v>
@@ -1851,7 +1851,7 @@
         <v>1339000</v>
       </c>
       <c r="F44" s="3">
-        <v>1121300</v>
+        <v>1121000</v>
       </c>
       <c r="G44" s="3">
         <v>919500</v>
@@ -1880,20 +1880,20 @@
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F45" s="3" t="s">
-        <v>3</v>
+      <c r="D45" s="3">
+        <v>30000</v>
+      </c>
+      <c r="E45" s="3">
+        <v>79000</v>
+      </c>
+      <c r="F45" s="3">
+        <v>23000</v>
       </c>
       <c r="G45" s="3">
-        <v>99100</v>
+        <v>50500</v>
       </c>
       <c r="H45" s="3">
-        <v>118800</v>
+        <v>40100</v>
       </c>
       <c r="I45" s="3" t="s">
         <v>3</v>
@@ -1923,7 +1923,7 @@
         <v>5800000</v>
       </c>
       <c r="F46" s="3">
-        <v>5291300</v>
+        <v>5291000</v>
       </c>
       <c r="G46" s="3">
         <v>2986700</v>
@@ -1953,19 +1953,19 @@
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>684000</v>
+        <v>474000</v>
       </c>
       <c r="E47" s="3">
-        <v>519000</v>
-      </c>
-      <c r="F47" s="3">
-        <v>53200</v>
+        <v>416000</v>
+      </c>
+      <c r="F47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="G47" s="3">
-        <v>115500</v>
+        <v>36700</v>
       </c>
       <c r="H47" s="3">
-        <v>271000</v>
+        <v>85500</v>
       </c>
       <c r="I47" s="3" t="s">
         <v>3</v>
@@ -2031,7 +2031,7 @@
         <v>363000</v>
       </c>
       <c r="F49" s="3">
-        <v>376700</v>
+        <v>377000</v>
       </c>
       <c r="G49" s="3">
         <v>547900</v>
@@ -2039,8 +2039,8 @@
       <c r="H49" s="3">
         <v>634800</v>
       </c>
-      <c r="I49" s="3" t="s">
-        <v>3</v>
+      <c r="I49" s="3">
+        <v>0</v>
       </c>
       <c r="J49" s="3" t="s">
         <v>3</v>
@@ -2133,19 +2133,19 @@
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>478000</v>
+        <v>447000</v>
       </c>
       <c r="E52" s="3">
-        <v>563000</v>
+        <v>374000</v>
       </c>
       <c r="F52" s="3">
-        <v>593400</v>
+        <v>294000</v>
       </c>
       <c r="G52" s="3">
-        <v>445200</v>
+        <v>80500</v>
       </c>
       <c r="H52" s="3">
-        <v>466300</v>
+        <v>118200</v>
       </c>
       <c r="I52" s="3" t="s">
         <v>3</v>
@@ -2211,7 +2211,7 @@
         <v>17841000</v>
       </c>
       <c r="F54" s="3">
-        <v>15027600</v>
+        <v>15028000</v>
       </c>
       <c r="G54" s="3">
         <v>12321600</v>
@@ -2279,13 +2279,13 @@
         <v>532000</v>
       </c>
       <c r="F57" s="3">
-        <v>551100</v>
+        <v>551000</v>
       </c>
       <c r="G57" s="3">
-        <v>600500</v>
+        <v>414500</v>
       </c>
       <c r="H57" s="3">
-        <v>559000</v>
+        <v>4000</v>
       </c>
       <c r="I57" s="3" t="s">
         <v>3</v>
@@ -2309,13 +2309,13 @@
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>603000</v>
+        <v>606000</v>
       </c>
       <c r="E58" s="3">
         <v>298000</v>
       </c>
       <c r="F58" s="3">
-        <v>432200</v>
+        <v>432000</v>
       </c>
       <c r="G58" s="3">
         <v>513100</v>
@@ -2323,8 +2323,8 @@
       <c r="H58" s="3">
         <v>817800</v>
       </c>
-      <c r="I58" s="3" t="s">
-        <v>3</v>
+      <c r="I58" s="3">
+        <v>0</v>
       </c>
       <c r="J58" s="3" t="s">
         <v>3</v>
@@ -2345,19 +2345,19 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>1985000</v>
+        <v>1486000</v>
       </c>
       <c r="E59" s="3">
-        <v>2529000</v>
+        <v>1956000</v>
       </c>
       <c r="F59" s="3">
-        <v>2179500</v>
+        <v>1577000</v>
       </c>
       <c r="G59" s="3">
-        <v>782500</v>
+        <v>497600</v>
       </c>
       <c r="H59" s="3">
-        <v>959300</v>
+        <v>955400</v>
       </c>
       <c r="I59" s="3" t="s">
         <v>3</v>
@@ -2387,7 +2387,7 @@
         <v>3359000</v>
       </c>
       <c r="F60" s="3">
-        <v>3162900</v>
+        <v>3163000</v>
       </c>
       <c r="G60" s="3">
         <v>1896100</v>
@@ -2420,13 +2420,13 @@
         <v>2151000</v>
       </c>
       <c r="E61" s="3">
-        <v>2558000</v>
+        <v>2561000</v>
       </c>
       <c r="F61" s="3">
-        <v>2006400</v>
+        <v>2015000</v>
       </c>
       <c r="G61" s="3">
-        <v>2289400</v>
+        <v>2322700</v>
       </c>
       <c r="H61" s="3">
         <v>2430500</v>
@@ -2453,19 +2453,19 @@
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>1643000</v>
+        <v>282000</v>
       </c>
       <c r="E62" s="3">
-        <v>1964000</v>
+        <v>315000</v>
       </c>
       <c r="F62" s="3">
-        <v>1825200</v>
+        <v>300000</v>
       </c>
       <c r="G62" s="3">
-        <v>894700</v>
+        <v>694000</v>
       </c>
       <c r="H62" s="3">
-        <v>711800</v>
+        <v>515100</v>
       </c>
       <c r="I62" s="3" t="s">
         <v>3</v>
@@ -2597,16 +2597,16 @@
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>6940000</v>
+        <v>6893000</v>
       </c>
       <c r="E66" s="3">
-        <v>7928000</v>
+        <v>7881000</v>
       </c>
       <c r="F66" s="3">
-        <v>7052100</v>
+        <v>6995000</v>
       </c>
       <c r="G66" s="3">
-        <v>5145300</v>
+        <v>5080100</v>
       </c>
       <c r="H66" s="3">
         <v>5478400</v>
@@ -2799,7 +2799,7 @@
         <v>-14021000</v>
       </c>
       <c r="F72" s="3">
-        <v>-15468800</v>
+        <v>-15469000</v>
       </c>
       <c r="G72" s="3">
         <v>-15218500</v>
@@ -2943,7 +2943,7 @@
         <v>9913000</v>
       </c>
       <c r="F76" s="3">
-        <v>7975500</v>
+        <v>7975000</v>
       </c>
       <c r="G76" s="3">
         <v>7176400</v>
@@ -3056,10 +3056,10 @@
         <v>1448000</v>
       </c>
       <c r="F81" s="3">
-        <v>-250300</v>
+        <v>-250000</v>
       </c>
       <c r="G81" s="3">
-        <v>-1347600</v>
+        <v>-1350000</v>
       </c>
       <c r="H81" s="3">
         <v>-1371200</v>
@@ -3102,22 +3102,22 @@
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>1451000</v>
+        <v>1322000</v>
       </c>
       <c r="E83" s="3">
-        <v>1623000</v>
+        <v>1447000</v>
       </c>
       <c r="F83" s="3">
-        <v>1618800</v>
+        <v>1411000</v>
       </c>
       <c r="G83" s="3">
-        <v>2522500</v>
+        <v>2238000</v>
       </c>
       <c r="H83" s="3">
-        <v>2678200</v>
+        <v>2435900</v>
       </c>
       <c r="I83" s="3">
-        <v>2947900</v>
+        <v>2683200</v>
       </c>
       <c r="J83" s="3" t="s">
         <v>3</v>
@@ -3327,7 +3327,7 @@
         <v>2839000</v>
       </c>
       <c r="G89" s="3">
-        <v>1005900</v>
+        <v>1004000</v>
       </c>
       <c r="H89" s="3">
         <v>496800</v>
@@ -3376,10 +3376,10 @@
         <v>-3059000</v>
       </c>
       <c r="F91" s="3">
-        <v>-1661600</v>
+        <v>-1767000</v>
       </c>
       <c r="G91" s="3">
-        <v>-449300</v>
+        <v>-592000</v>
       </c>
       <c r="H91" s="3">
         <v>-587900</v>
@@ -3484,10 +3484,10 @@
         <v>-4058000</v>
       </c>
       <c r="F94" s="3">
-        <v>-1450300</v>
+        <v>-1450000</v>
       </c>
       <c r="G94" s="3">
-        <v>-366200</v>
+        <v>-366000</v>
       </c>
       <c r="H94" s="3">
         <v>343700</v>
@@ -3680,10 +3680,10 @@
         <v>842000</v>
       </c>
       <c r="F100" s="3">
-        <v>650400</v>
+        <v>650000</v>
       </c>
       <c r="G100" s="3">
-        <v>-732700</v>
+        <v>-733000</v>
       </c>
       <c r="H100" s="3">
         <v>-683800</v>
@@ -3716,10 +3716,10 @@
         <v>5000</v>
       </c>
       <c r="F101" s="3">
-        <v>-8100</v>
+        <v>-8000</v>
       </c>
       <c r="G101" s="3">
-        <v>3800</v>
+        <v>6000</v>
       </c>
       <c r="H101" s="3">
         <v>-3400</v>
@@ -3752,10 +3752,10 @@
         <v>-587000</v>
       </c>
       <c r="F102" s="3">
-        <v>2031100</v>
+        <v>2031000</v>
       </c>
       <c r="G102" s="3">
-        <v>-89200</v>
+        <v>-89000</v>
       </c>
       <c r="H102" s="3">
         <v>153300</v>
@@ -3763,8 +3763,8 @@
       <c r="I102" s="3">
         <v>242900</v>
       </c>
-      <c r="J102" s="3" t="s">
-        <v>3</v>
+      <c r="J102" s="3">
+        <v>0</v>
       </c>
       <c r="K102" s="3" t="s">
         <v>3</v>

--- a/AAII_Financials/Yearly/GFS_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/GFS_YR_FIN.xlsx
@@ -656,53 +656,53 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:N102"/>
+  <dimension ref="A5:O102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="8" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="13" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="9" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="14" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E7" s="2">
         <v>45291</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>44926</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44561</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44196</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>43830</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43465</v>
       </c>
-      <c r="J7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="K7" s="2" t="s">
         <v>3</v>
       </c>
@@ -712,33 +712,36 @@
       <c r="M7" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="N7" s="2"/>
-    </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N7" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="O7" s="2"/>
+    </row>
+    <row r="8" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>6750000</v>
+      </c>
+      <c r="E8" s="3">
         <v>7392000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>8108000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>6585000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>4851000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>5812800</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>6196000</v>
       </c>
-      <c r="J8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K8" s="3" t="s">
         <v>3</v>
       </c>
@@ -748,33 +751,36 @@
       <c r="M8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N8" s="3"/>
-    </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O8" s="3"/>
+    </row>
+    <row r="9" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>5099000</v>
+      </c>
+      <c r="E9" s="3">
         <v>5291000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>5869000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>5572000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>5563000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>6345000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>6646100</v>
       </c>
-      <c r="J9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K9" s="3" t="s">
         <v>3</v>
       </c>
@@ -784,33 +790,36 @@
       <c r="M9" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N9" s="3"/>
-    </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O9" s="3"/>
+    </row>
+    <row r="10" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>1651000</v>
+      </c>
+      <c r="E10" s="3">
         <v>2101000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>2239000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>1013000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>-712000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>-532200</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>-450100</v>
       </c>
-      <c r="J10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K10" s="3" t="s">
         <v>3</v>
       </c>
@@ -820,9 +829,12 @@
       <c r="M10" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N10" s="3"/>
-    </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O10" s="3"/>
+    </row>
+    <row r="11" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -837,32 +849,33 @@
       <c r="L11" s="3"/>
       <c r="M11" s="3"/>
       <c r="N11" s="3"/>
-    </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O11" s="3"/>
+    </row>
+    <row r="12" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>496000</v>
+      </c>
+      <c r="E12" s="3">
         <v>428000</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>482000</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>478000</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>476000</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>583000</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>926200</v>
       </c>
-      <c r="J12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K12" s="3" t="s">
         <v>3</v>
       </c>
@@ -872,9 +885,12 @@
       <c r="M12" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N12" s="3"/>
-    </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O12" s="3"/>
+    </row>
+    <row r="13" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -908,33 +924,36 @@
       <c r="M13" s="3">
         <v>0</v>
       </c>
-      <c r="N13" s="3"/>
-    </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N13" s="3">
+        <v>0</v>
+      </c>
+      <c r="O13" s="3"/>
+    </row>
+    <row r="14" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>853000</v>
+      </c>
+      <c r="E14" s="3">
         <v>84000</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>-412000</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>-39000</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>-449000</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>-624700</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>632900</v>
       </c>
-      <c r="J14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K14" s="3" t="s">
         <v>3</v>
       </c>
@@ -944,35 +963,38 @@
       <c r="M14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N14" s="3"/>
-    </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O14" s="3"/>
+    </row>
+    <row r="15" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>1493000</v>
+      </c>
+      <c r="E15" s="3">
         <v>1387000</v>
       </c>
-      <c r="E15" s="3">
-        <v>1531000</v>
-      </c>
       <c r="F15" s="3">
+        <v>1541000</v>
+      </c>
+      <c r="G15" s="3">
         <v>1537000</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>2522000</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>2678200</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>2947900</v>
       </c>
-      <c r="J15" s="3">
-        <v>0</v>
-      </c>
-      <c r="K15" s="3" t="s">
-        <v>3</v>
+      <c r="K15" s="3">
+        <v>0</v>
       </c>
       <c r="L15" s="3" t="s">
         <v>3</v>
@@ -980,9 +1002,12 @@
       <c r="M15" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N15" s="3"/>
-    </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N15" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O15" s="3"/>
+    </row>
+    <row r="16" spans="1:15" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -994,32 +1019,33 @@
       <c r="L16" s="3"/>
       <c r="M16" s="3"/>
       <c r="N16" s="3"/>
-    </row>
-    <row r="17" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O16" s="3"/>
+    </row>
+    <row r="17" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>6022000</v>
+      </c>
+      <c r="E17" s="3">
         <v>6192000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>6847000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>6645000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>6484000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>7373600</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>8025100</v>
       </c>
-      <c r="J17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K17" s="3" t="s">
         <v>3</v>
       </c>
@@ -1029,33 +1055,36 @@
       <c r="M17" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N17" s="3"/>
-    </row>
-    <row r="18" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O17" s="3"/>
+    </row>
+    <row r="18" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>728000</v>
+      </c>
+      <c r="E18" s="3">
         <v>1200000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>1261000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-60000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-1633000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-1560800</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-1829000</v>
       </c>
-      <c r="J18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1065,9 +1094,12 @@
       <c r="M18" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N18" s="3"/>
-    </row>
-    <row r="19" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O18" s="3"/>
+    </row>
+    <row r="19" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1082,32 +1114,33 @@
       <c r="L19" s="3"/>
       <c r="M19" s="3"/>
       <c r="N19" s="3"/>
-    </row>
-    <row r="20" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O19" s="3"/>
+    </row>
+    <row r="20" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>106000</v>
+      </c>
+      <c r="E20" s="3">
         <v>53000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>88000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>57000</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>51000</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>19500</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>20400</v>
       </c>
-      <c r="J20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K20" s="3" t="s">
         <v>3</v>
       </c>
@@ -1117,35 +1150,38 @@
       <c r="M20" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N20" s="3"/>
-    </row>
-    <row r="21" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O20" s="3"/>
+    </row>
+    <row r="21" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>2115000</v>
+      </c>
+      <c r="E21" s="3">
         <v>2534000</v>
       </c>
-      <c r="E21" s="3">
-        <v>2704000</v>
-      </c>
       <c r="F21" s="3">
+        <v>2714000</v>
+      </c>
+      <c r="G21" s="3">
         <v>1420000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>838000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>1097800</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>1098500</v>
       </c>
-      <c r="J21" s="3">
-        <v>0</v>
-      </c>
-      <c r="K21" s="3" t="s">
-        <v>3</v>
+      <c r="K21" s="3">
+        <v>0</v>
       </c>
       <c r="L21" s="3" t="s">
         <v>3</v>
@@ -1153,33 +1189,36 @@
       <c r="M21" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N21" s="3"/>
-    </row>
-    <row r="22" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O21" s="3"/>
+    </row>
+    <row r="22" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>106000</v>
+      </c>
+      <c r="E22" s="3">
         <v>101000</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>92000</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>99000</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>133000</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>202800</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>137500</v>
       </c>
-      <c r="J22" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K22" s="3" t="s">
         <v>3</v>
       </c>
@@ -1189,33 +1228,36 @@
       <c r="M22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N22" s="3"/>
-    </row>
-    <row r="23" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O22" s="3"/>
+    </row>
+    <row r="23" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-170000</v>
+      </c>
+      <c r="E23" s="3">
         <v>1084000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>1532000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-176000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-1365000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-1147100</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-2609600</v>
       </c>
-      <c r="J23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K23" s="3" t="s">
         <v>3</v>
       </c>
@@ -1225,33 +1267,36 @@
       <c r="M23" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N23" s="3"/>
-    </row>
-    <row r="24" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O23" s="3"/>
+    </row>
+    <row r="24" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>92000</v>
+      </c>
+      <c r="E24" s="3">
         <v>66000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>86000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>78000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>-12000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>224100</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>16400</v>
       </c>
-      <c r="J24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K24" s="3" t="s">
         <v>3</v>
       </c>
@@ -1261,9 +1306,12 @@
       <c r="M24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N24" s="3"/>
-    </row>
-    <row r="25" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O24" s="3"/>
+    </row>
+    <row r="25" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1297,33 +1345,36 @@
       <c r="M25" s="3">
         <v>0</v>
       </c>
-      <c r="N25" s="3"/>
-    </row>
-    <row r="26" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N25" s="3">
+        <v>0</v>
+      </c>
+      <c r="O25" s="3"/>
+    </row>
+    <row r="26" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-262000</v>
+      </c>
+      <c r="E26" s="3">
         <v>1018000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>1446000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-254000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-1353000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-1371200</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-2626000</v>
       </c>
-      <c r="J26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K26" s="3" t="s">
         <v>3</v>
       </c>
@@ -1333,33 +1384,36 @@
       <c r="M26" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N26" s="3"/>
-    </row>
-    <row r="27" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O26" s="3"/>
+    </row>
+    <row r="27" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-265000</v>
+      </c>
+      <c r="E27" s="3">
         <v>1020000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>1448000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-250000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-1350000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-1371200</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-2701600</v>
       </c>
-      <c r="J27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K27" s="3" t="s">
         <v>3</v>
       </c>
@@ -1369,9 +1423,12 @@
       <c r="M27" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N27" s="3"/>
-    </row>
-    <row r="28" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O27" s="3"/>
+    </row>
+    <row r="28" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1405,9 +1462,12 @@
       <c r="M28" s="3">
         <v>0</v>
       </c>
-      <c r="N28" s="3"/>
-    </row>
-    <row r="29" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N28" s="3">
+        <v>0</v>
+      </c>
+      <c r="O28" s="3"/>
+    </row>
+    <row r="29" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1427,13 +1487,13 @@
         <v>0</v>
       </c>
       <c r="I29" s="3">
+        <v>0</v>
+      </c>
+      <c r="J29" s="3">
         <v>-148000</v>
       </c>
-      <c r="J29" s="3">
-        <v>0</v>
-      </c>
-      <c r="K29" s="3" t="s">
-        <v>3</v>
+      <c r="K29" s="3">
+        <v>0</v>
       </c>
       <c r="L29" s="3" t="s">
         <v>3</v>
@@ -1441,9 +1501,12 @@
       <c r="M29" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N29" s="3"/>
-    </row>
-    <row r="30" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N29" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O29" s="3"/>
+    </row>
+    <row r="30" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1477,9 +1540,12 @@
       <c r="M30" s="3">
         <v>0</v>
       </c>
-      <c r="N30" s="3"/>
-    </row>
-    <row r="31" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N30" s="3">
+        <v>0</v>
+      </c>
+      <c r="O30" s="3"/>
+    </row>
+    <row r="31" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1513,33 +1579,36 @@
       <c r="M31" s="3">
         <v>0</v>
       </c>
-      <c r="N31" s="3"/>
-    </row>
-    <row r="32" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N31" s="3">
+        <v>0</v>
+      </c>
+      <c r="O31" s="3"/>
+    </row>
+    <row r="32" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-106000</v>
+      </c>
+      <c r="E32" s="3">
         <v>-53000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-88000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-57000</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-51000</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-19500</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-20400</v>
       </c>
-      <c r="J32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K32" s="3" t="s">
         <v>3</v>
       </c>
@@ -1549,33 +1618,36 @@
       <c r="M32" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N32" s="3"/>
-    </row>
-    <row r="33" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O32" s="3"/>
+    </row>
+    <row r="33" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-265000</v>
+      </c>
+      <c r="E33" s="3">
         <v>1020000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>1448000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-250000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-1350000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-1371200</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-2701600</v>
       </c>
-      <c r="J33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K33" s="3" t="s">
         <v>3</v>
       </c>
@@ -1585,9 +1657,12 @@
       <c r="M33" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N33" s="3"/>
-    </row>
-    <row r="34" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O33" s="3"/>
+    </row>
+    <row r="34" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1621,33 +1696,36 @@
       <c r="M34" s="3">
         <v>0</v>
       </c>
-      <c r="N34" s="3"/>
-    </row>
-    <row r="35" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N34" s="3">
+        <v>0</v>
+      </c>
+      <c r="O34" s="3"/>
+    </row>
+    <row r="35" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-265000</v>
+      </c>
+      <c r="E35" s="3">
         <v>1020000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>1448000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-250000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-1350000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-1371200</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-2701600</v>
       </c>
-      <c r="J35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K35" s="3" t="s">
         <v>3</v>
       </c>
@@ -1657,38 +1735,41 @@
       <c r="M35" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N35" s="3"/>
-    </row>
-    <row r="37" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O35" s="3"/>
+    </row>
+    <row r="37" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E38" s="2">
         <v>45291</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>44926</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44561</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44196</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>43830</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43465</v>
       </c>
-      <c r="J38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="K38" s="2" t="s">
         <v>3</v>
       </c>
@@ -1698,9 +1779,12 @@
       <c r="M38" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="N38" s="2"/>
-    </row>
-    <row r="39" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N38" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="O38" s="2"/>
+    </row>
+    <row r="39" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1715,8 +1799,9 @@
       <c r="L39" s="3"/>
       <c r="M39" s="3"/>
       <c r="N39" s="3"/>
-    </row>
-    <row r="40" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O39" s="3"/>
+    </row>
+    <row r="40" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1731,29 +1816,30 @@
       <c r="L40" s="3"/>
       <c r="M40" s="3"/>
       <c r="N40" s="3"/>
-    </row>
-    <row r="41" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O40" s="3"/>
+    </row>
+    <row r="41" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>2192000</v>
+      </c>
+      <c r="E41" s="3">
         <v>2387000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>2352000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>2939000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>908100</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>997300</v>
       </c>
-      <c r="I41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J41" s="3" t="s">
         <v>3</v>
       </c>
@@ -1766,21 +1852,24 @@
       <c r="M41" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N41" s="3"/>
-    </row>
-    <row r="42" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O41" s="3"/>
+    </row>
+    <row r="42" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>1194000</v>
+      </c>
+      <c r="E42" s="3">
         <v>1055000</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>622000</v>
       </c>
-      <c r="F42" s="3">
-        <v>0</v>
-      </c>
       <c r="G42" s="3">
         <v>0</v>
       </c>
@@ -1793,8 +1882,8 @@
       <c r="J42" s="3">
         <v>0</v>
       </c>
-      <c r="K42" s="3" t="s">
-        <v>3</v>
+      <c r="K42" s="3">
+        <v>0</v>
       </c>
       <c r="L42" s="3" t="s">
         <v>3</v>
@@ -1802,30 +1891,33 @@
       <c r="M42" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N42" s="3"/>
-    </row>
-    <row r="43" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N42" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O42" s="3"/>
+    </row>
+    <row r="43" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>1393000</v>
+      </c>
+      <c r="E43" s="3">
         <v>1368000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>1408000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>1208000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>1108600</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>2065400</v>
       </c>
-      <c r="I43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J43" s="3" t="s">
         <v>3</v>
       </c>
@@ -1838,30 +1930,33 @@
       <c r="M43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N43" s="3"/>
-    </row>
-    <row r="44" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O43" s="3"/>
+    </row>
+    <row r="44" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>1624000</v>
+      </c>
+      <c r="E44" s="3">
         <v>1487000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>1339000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>1121000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>919500</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>351900</v>
       </c>
-      <c r="I44" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J44" s="3" t="s">
         <v>3</v>
       </c>
@@ -1874,30 +1969,33 @@
       <c r="M44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N44" s="3"/>
-    </row>
-    <row r="45" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O44" s="3"/>
+    </row>
+    <row r="45" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>13000</v>
+      </c>
+      <c r="E45" s="3">
         <v>30000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>79000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>23000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>50500</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>40100</v>
       </c>
-      <c r="I45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J45" s="3" t="s">
         <v>3</v>
       </c>
@@ -1910,30 +2008,33 @@
       <c r="M45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N45" s="3"/>
-    </row>
-    <row r="46" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O45" s="3"/>
+    </row>
+    <row r="46" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>6416000</v>
+      </c>
+      <c r="E46" s="3">
         <v>6327000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>5800000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>5291000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>2986700</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>3514200</v>
       </c>
-      <c r="I46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J46" s="3" t="s">
         <v>3</v>
       </c>
@@ -1946,30 +2047,33 @@
       <c r="M46" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N46" s="3"/>
-    </row>
-    <row r="47" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O46" s="3"/>
+    </row>
+    <row r="47" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>474000</v>
+        <v>890000</v>
       </c>
       <c r="E47" s="3">
+        <v>547000</v>
+      </c>
+      <c r="F47" s="3">
         <v>416000</v>
       </c>
-      <c r="F47" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G47" s="3">
+      <c r="G47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H47" s="3">
         <v>36700</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>85500</v>
       </c>
-      <c r="I47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J47" s="3" t="s">
         <v>3</v>
       </c>
@@ -1982,30 +2086,33 @@
       <c r="M47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N47" s="3"/>
-    </row>
-    <row r="48" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O47" s="3"/>
+    </row>
+    <row r="48" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>8260000</v>
+      </c>
+      <c r="E48" s="3">
         <v>10164000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>10596000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>8713000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>8226200</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>9611300</v>
       </c>
-      <c r="I48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J48" s="3" t="s">
         <v>3</v>
       </c>
@@ -2018,32 +2125,35 @@
       <c r="M48" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N48" s="3"/>
-    </row>
-    <row r="49" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O48" s="3"/>
+    </row>
+    <row r="49" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>660000</v>
+      </c>
+      <c r="E49" s="3">
         <v>391000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>363000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>377000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>547900</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>634800</v>
       </c>
-      <c r="I49" s="3">
-        <v>0</v>
-      </c>
-      <c r="J49" s="3" t="s">
-        <v>3</v>
+      <c r="J49" s="3">
+        <v>0</v>
       </c>
       <c r="K49" s="3" t="s">
         <v>3</v>
@@ -2054,9 +2164,12 @@
       <c r="M49" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N49" s="3"/>
-    </row>
-    <row r="50" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N49" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O49" s="3"/>
+    </row>
+    <row r="50" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2090,9 +2203,12 @@
       <c r="M50" s="3">
         <v>0</v>
       </c>
-      <c r="N50" s="3"/>
-    </row>
-    <row r="51" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N50" s="3">
+        <v>0</v>
+      </c>
+      <c r="O50" s="3"/>
+    </row>
+    <row r="51" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2126,30 +2242,33 @@
       <c r="M51" s="3">
         <v>0</v>
       </c>
-      <c r="N51" s="3"/>
-    </row>
-    <row r="52" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N51" s="3">
+        <v>0</v>
+      </c>
+      <c r="O51" s="3"/>
+    </row>
+    <row r="52" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>447000</v>
+        <v>385000</v>
       </c>
       <c r="E52" s="3">
         <v>374000</v>
       </c>
       <c r="F52" s="3">
+        <v>374000</v>
+      </c>
+      <c r="G52" s="3">
         <v>294000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>80500</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>118200</v>
       </c>
-      <c r="I52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J52" s="3" t="s">
         <v>3</v>
       </c>
@@ -2162,9 +2281,12 @@
       <c r="M52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N52" s="3"/>
-    </row>
-    <row r="53" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O52" s="3"/>
+    </row>
+    <row r="53" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2198,30 +2320,33 @@
       <c r="M53" s="3">
         <v>0</v>
       </c>
-      <c r="N53" s="3"/>
-    </row>
-    <row r="54" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N53" s="3">
+        <v>0</v>
+      </c>
+      <c r="O53" s="3"/>
+    </row>
+    <row r="54" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>16799000</v>
+      </c>
+      <c r="E54" s="3">
         <v>18044000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>17841000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>15028000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>12321600</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>14497500</v>
       </c>
-      <c r="I54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J54" s="3" t="s">
         <v>3</v>
       </c>
@@ -2234,9 +2359,12 @@
       <c r="M54" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N54" s="3"/>
-    </row>
-    <row r="55" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O54" s="3"/>
+    </row>
+    <row r="55" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2251,8 +2379,9 @@
       <c r="L55" s="3"/>
       <c r="M55" s="3"/>
       <c r="N55" s="3"/>
-    </row>
-    <row r="56" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O55" s="3"/>
+    </row>
+    <row r="56" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2267,29 +2396,30 @@
       <c r="L56" s="3"/>
       <c r="M56" s="3"/>
       <c r="N56" s="3"/>
-    </row>
-    <row r="57" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O56" s="3"/>
+    </row>
+    <row r="57" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>406000</v>
+      </c>
+      <c r="E57" s="3">
         <v>511000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>532000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>551000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>414500</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>4000</v>
       </c>
-      <c r="I57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J57" s="3" t="s">
         <v>3</v>
       </c>
@@ -2302,32 +2432,35 @@
       <c r="M57" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N57" s="3"/>
-    </row>
-    <row r="58" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O57" s="3"/>
+    </row>
+    <row r="58" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>843000</v>
+      </c>
+      <c r="E58" s="3">
         <v>606000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>298000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>432000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>513100</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>817800</v>
       </c>
-      <c r="I58" s="3">
-        <v>0</v>
-      </c>
-      <c r="J58" s="3" t="s">
-        <v>3</v>
+      <c r="J58" s="3">
+        <v>0</v>
       </c>
       <c r="K58" s="3" t="s">
         <v>3</v>
@@ -2338,30 +2471,33 @@
       <c r="M58" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N58" s="3"/>
-    </row>
-    <row r="59" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O58" s="3"/>
+    </row>
+    <row r="59" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>1273000</v>
+      </c>
+      <c r="E59" s="3">
         <v>1486000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>1956000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>1577000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>497600</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>955400</v>
       </c>
-      <c r="I59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J59" s="3" t="s">
         <v>3</v>
       </c>
@@ -2374,30 +2510,33 @@
       <c r="M59" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N59" s="3"/>
-    </row>
-    <row r="60" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O59" s="3"/>
+    </row>
+    <row r="60" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>3044000</v>
+      </c>
+      <c r="E60" s="3">
         <v>3099000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>3359000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>3163000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>1896100</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>2336100</v>
       </c>
-      <c r="I60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J60" s="3" t="s">
         <v>3</v>
       </c>
@@ -2410,30 +2549,33 @@
       <c r="M60" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N60" s="3"/>
-    </row>
-    <row r="61" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O60" s="3"/>
+    </row>
+    <row r="61" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>1478000</v>
+      </c>
+      <c r="E61" s="3">
         <v>2151000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>2561000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>2015000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>2322700</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>2430500</v>
       </c>
-      <c r="I61" s="3">
-        <v>0</v>
-      </c>
       <c r="J61" s="3">
         <v>0</v>
       </c>
@@ -2446,30 +2588,33 @@
       <c r="M61" s="3">
         <v>0</v>
       </c>
-      <c r="N61" s="3"/>
-    </row>
-    <row r="62" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N61" s="3">
+        <v>0</v>
+      </c>
+      <c r="O61" s="3"/>
+    </row>
+    <row r="62" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>449000</v>
+      </c>
+      <c r="E62" s="3">
         <v>282000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>315000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>300000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>694000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>515100</v>
       </c>
-      <c r="I62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J62" s="3" t="s">
         <v>3</v>
       </c>
@@ -2482,9 +2627,12 @@
       <c r="M62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N62" s="3"/>
-    </row>
-    <row r="63" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O62" s="3"/>
+    </row>
+    <row r="63" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2518,9 +2666,12 @@
       <c r="M63" s="3">
         <v>0</v>
       </c>
-      <c r="N63" s="3"/>
-    </row>
-    <row r="64" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N63" s="3">
+        <v>0</v>
+      </c>
+      <c r="O63" s="3"/>
+    </row>
+    <row r="64" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2554,9 +2705,12 @@
       <c r="M64" s="3">
         <v>0</v>
       </c>
-      <c r="N64" s="3"/>
-    </row>
-    <row r="65" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N64" s="3">
+        <v>0</v>
+      </c>
+      <c r="O64" s="3"/>
+    </row>
+    <row r="65" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2590,30 +2744,33 @@
       <c r="M65" s="3">
         <v>0</v>
       </c>
-      <c r="N65" s="3"/>
-    </row>
-    <row r="66" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N65" s="3">
+        <v>0</v>
+      </c>
+      <c r="O65" s="3"/>
+    </row>
+    <row r="66" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>5975000</v>
+      </c>
+      <c r="E66" s="3">
         <v>6893000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>7881000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>6995000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>5080100</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>5478400</v>
       </c>
-      <c r="I66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J66" s="3" t="s">
         <v>3</v>
       </c>
@@ -2626,9 +2783,12 @@
       <c r="M66" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N66" s="3"/>
-    </row>
-    <row r="67" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O66" s="3"/>
+    </row>
+    <row r="67" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2643,8 +2803,9 @@
       <c r="L67" s="3"/>
       <c r="M67" s="3"/>
       <c r="N67" s="3"/>
-    </row>
-    <row r="68" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O67" s="3"/>
+    </row>
+    <row r="68" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2678,9 +2839,12 @@
       <c r="M68" s="3">
         <v>0</v>
       </c>
-      <c r="N68" s="3"/>
-    </row>
-    <row r="69" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N68" s="3">
+        <v>0</v>
+      </c>
+      <c r="O68" s="3"/>
+    </row>
+    <row r="69" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2714,9 +2878,12 @@
       <c r="M69" s="3">
         <v>0</v>
       </c>
-      <c r="N69" s="3"/>
-    </row>
-    <row r="70" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N69" s="3">
+        <v>0</v>
+      </c>
+      <c r="O69" s="3"/>
+    </row>
+    <row r="70" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -2750,9 +2917,12 @@
       <c r="M70" s="3">
         <v>0</v>
       </c>
-      <c r="N70" s="3"/>
-    </row>
-    <row r="71" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N70" s="3">
+        <v>0</v>
+      </c>
+      <c r="O70" s="3"/>
+    </row>
+    <row r="71" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -2786,30 +2956,33 @@
       <c r="M71" s="3">
         <v>0</v>
       </c>
-      <c r="N71" s="3"/>
-    </row>
-    <row r="72" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N71" s="3">
+        <v>0</v>
+      </c>
+      <c r="O71" s="3"/>
+    </row>
+    <row r="72" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-13266000</v>
+      </c>
+      <c r="E72" s="3">
         <v>-13001000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-14021000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-15469000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-15218500</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-13870900</v>
       </c>
-      <c r="I72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J72" s="3" t="s">
         <v>3</v>
       </c>
@@ -2822,9 +2995,12 @@
       <c r="M72" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N72" s="3"/>
-    </row>
-    <row r="73" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O72" s="3"/>
+    </row>
+    <row r="73" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -2858,9 +3034,12 @@
       <c r="M73" s="3">
         <v>0</v>
       </c>
-      <c r="N73" s="3"/>
-    </row>
-    <row r="74" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N73" s="3">
+        <v>0</v>
+      </c>
+      <c r="O73" s="3"/>
+    </row>
+    <row r="74" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -2894,9 +3073,12 @@
       <c r="M74" s="3">
         <v>0</v>
       </c>
-      <c r="N74" s="3"/>
-    </row>
-    <row r="75" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N74" s="3">
+        <v>0</v>
+      </c>
+      <c r="O74" s="3"/>
+    </row>
+    <row r="75" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -2930,30 +3112,33 @@
       <c r="M75" s="3">
         <v>0</v>
       </c>
-      <c r="N75" s="3"/>
-    </row>
-    <row r="76" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N75" s="3">
+        <v>0</v>
+      </c>
+      <c r="O75" s="3"/>
+    </row>
+    <row r="76" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>10776000</v>
+      </c>
+      <c r="E76" s="3">
         <v>11104000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>9913000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>7975000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>7176400</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>9019100</v>
       </c>
-      <c r="I76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J76" s="3" t="s">
         <v>3</v>
       </c>
@@ -2966,9 +3151,12 @@
       <c r="M76" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N76" s="3"/>
-    </row>
-    <row r="77" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O76" s="3"/>
+    </row>
+    <row r="77" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3002,38 +3190,41 @@
       <c r="M77" s="3">
         <v>0</v>
       </c>
-      <c r="N77" s="3"/>
-    </row>
-    <row r="79" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N77" s="3">
+        <v>0</v>
+      </c>
+      <c r="O77" s="3"/>
+    </row>
+    <row r="79" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E80" s="2">
         <v>45291</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>44926</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44561</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44196</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>43830</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43465</v>
       </c>
-      <c r="J80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="K80" s="2" t="s">
         <v>3</v>
       </c>
@@ -3043,33 +3234,36 @@
       <c r="M80" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="N80" s="2"/>
-    </row>
-    <row r="81" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N80" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="O80" s="2"/>
+    </row>
+    <row r="81" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-265000</v>
+      </c>
+      <c r="E81" s="3">
         <v>1020000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>1448000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-250000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-1350000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-1371200</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-2701600</v>
       </c>
-      <c r="J81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K81" s="3" t="s">
         <v>3</v>
       </c>
@@ -3079,9 +3273,12 @@
       <c r="M81" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N81" s="3"/>
-    </row>
-    <row r="82" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O81" s="3"/>
+    </row>
+    <row r="82" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3096,32 +3293,33 @@
       <c r="L82" s="3"/>
       <c r="M82" s="3"/>
       <c r="N82" s="3"/>
-    </row>
-    <row r="83" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O82" s="3"/>
+    </row>
+    <row r="83" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>1442000</v>
+      </c>
+      <c r="E83" s="3">
         <v>1322000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>1447000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>1411000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>2238000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>2435900</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>2683200</v>
       </c>
-      <c r="J83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K83" s="3" t="s">
         <v>3</v>
       </c>
@@ -3131,9 +3329,12 @@
       <c r="M83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N83" s="3"/>
-    </row>
-    <row r="84" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O83" s="3"/>
+    </row>
+    <row r="84" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3167,9 +3368,12 @@
       <c r="M84" s="3">
         <v>0</v>
       </c>
-      <c r="N84" s="3"/>
-    </row>
-    <row r="85" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N84" s="3">
+        <v>0</v>
+      </c>
+      <c r="O84" s="3"/>
+    </row>
+    <row r="85" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3203,9 +3407,12 @@
       <c r="M85" s="3">
         <v>0</v>
       </c>
-      <c r="N85" s="3"/>
-    </row>
-    <row r="86" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N85" s="3">
+        <v>0</v>
+      </c>
+      <c r="O85" s="3"/>
+    </row>
+    <row r="86" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3239,9 +3446,12 @@
       <c r="M86" s="3">
         <v>0</v>
       </c>
-      <c r="N86" s="3"/>
-    </row>
-    <row r="87" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N86" s="3">
+        <v>0</v>
+      </c>
+      <c r="O86" s="3"/>
+    </row>
+    <row r="87" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3275,9 +3485,12 @@
       <c r="M87" s="3">
         <v>0</v>
       </c>
-      <c r="N87" s="3"/>
-    </row>
-    <row r="88" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N87" s="3">
+        <v>0</v>
+      </c>
+      <c r="O87" s="3"/>
+    </row>
+    <row r="88" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3311,33 +3524,36 @@
       <c r="M88" s="3">
         <v>0</v>
       </c>
-      <c r="N88" s="3"/>
-    </row>
-    <row r="89" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N88" s="3">
+        <v>0</v>
+      </c>
+      <c r="O88" s="3"/>
+    </row>
+    <row r="89" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>1722000</v>
+      </c>
+      <c r="E89" s="3">
         <v>2125000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>2624000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>2839000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>1004000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>496800</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>279300</v>
       </c>
-      <c r="J89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K89" s="3" t="s">
         <v>3</v>
       </c>
@@ -3347,9 +3563,12 @@
       <c r="M89" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N89" s="3"/>
-    </row>
-    <row r="90" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O89" s="3"/>
+    </row>
+    <row r="90" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3364,32 +3583,33 @@
       <c r="L90" s="3"/>
       <c r="M90" s="3"/>
       <c r="N90" s="3"/>
-    </row>
-    <row r="91" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O90" s="3"/>
+    </row>
+    <row r="91" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-625000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-1804000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-3059000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-1767000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-592000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-587900</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-1150300</v>
       </c>
-      <c r="J91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K91" s="3" t="s">
         <v>3</v>
       </c>
@@ -3399,9 +3619,12 @@
       <c r="M91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N91" s="3"/>
-    </row>
-    <row r="92" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O91" s="3"/>
+    </row>
+    <row r="92" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3435,9 +3658,12 @@
       <c r="M92" s="3">
         <v>0</v>
       </c>
-      <c r="N92" s="3"/>
-    </row>
-    <row r="93" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N92" s="3">
+        <v>0</v>
+      </c>
+      <c r="O92" s="3"/>
+    </row>
+    <row r="93" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3471,33 +3697,36 @@
       <c r="M93" s="3">
         <v>0</v>
       </c>
-      <c r="N93" s="3"/>
-    </row>
-    <row r="94" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N93" s="3">
+        <v>0</v>
+      </c>
+      <c r="O93" s="3"/>
+    </row>
+    <row r="94" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-1125000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-1882000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-4058000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-1450000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-366000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>343700</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-1167200</v>
       </c>
-      <c r="J94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K94" s="3" t="s">
         <v>3</v>
       </c>
@@ -3507,9 +3736,12 @@
       <c r="M94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N94" s="3"/>
-    </row>
-    <row r="95" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O94" s="3"/>
+    </row>
+    <row r="95" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3524,8 +3756,9 @@
       <c r="L95" s="3"/>
       <c r="M95" s="3"/>
       <c r="N95" s="3"/>
-    </row>
-    <row r="96" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O95" s="3"/>
+    </row>
+    <row r="96" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -3559,9 +3792,12 @@
       <c r="M96" s="3">
         <v>0</v>
       </c>
-      <c r="N96" s="3"/>
-    </row>
-    <row r="97" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N96" s="3">
+        <v>0</v>
+      </c>
+      <c r="O96" s="3"/>
+    </row>
+    <row r="97" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3595,9 +3831,12 @@
       <c r="M97" s="3">
         <v>0</v>
       </c>
-      <c r="N97" s="3"/>
-    </row>
-    <row r="98" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N97" s="3">
+        <v>0</v>
+      </c>
+      <c r="O97" s="3"/>
+    </row>
+    <row r="98" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -3631,9 +3870,12 @@
       <c r="M98" s="3">
         <v>0</v>
       </c>
-      <c r="N98" s="3"/>
-    </row>
-    <row r="99" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N98" s="3">
+        <v>0</v>
+      </c>
+      <c r="O98" s="3"/>
+    </row>
+    <row r="99" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -3667,33 +3909,36 @@
       <c r="M99" s="3">
         <v>0</v>
       </c>
-      <c r="N99" s="3"/>
-    </row>
-    <row r="100" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N99" s="3">
+        <v>0</v>
+      </c>
+      <c r="O99" s="3"/>
+    </row>
+    <row r="100" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-785000</v>
+      </c>
+      <c r="E100" s="3">
         <v>-212000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>842000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>650000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-733000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-683800</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>1132100</v>
       </c>
-      <c r="J100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K100" s="3" t="s">
         <v>3</v>
       </c>
@@ -3703,33 +3948,36 @@
       <c r="M100" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N100" s="3"/>
-    </row>
-    <row r="101" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O100" s="3"/>
+    </row>
+    <row r="101" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-7000</v>
+      </c>
+      <c r="E101" s="3">
         <v>4000</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>5000</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-8000</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>6000</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-3400</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-1300</v>
       </c>
-      <c r="J101" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K101" s="3" t="s">
         <v>3</v>
       </c>
@@ -3739,35 +3987,38 @@
       <c r="M101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N101" s="3"/>
-    </row>
-    <row r="102" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O101" s="3"/>
+    </row>
+    <row r="102" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-195000</v>
+      </c>
+      <c r="E102" s="3">
         <v>35000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-587000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>2031000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-89000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>153300</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>242900</v>
       </c>
-      <c r="J102" s="3">
-        <v>0</v>
-      </c>
-      <c r="K102" s="3" t="s">
-        <v>3</v>
+      <c r="K102" s="3">
+        <v>0</v>
       </c>
       <c r="L102" s="3" t="s">
         <v>3</v>
@@ -3775,7 +4026,10 @@
       <c r="M102" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N102" s="3"/>
+      <c r="N102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/AAII_Financials/Yearly/GFS_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/GFS_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="303" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="305" uniqueCount="92">
   <si>
     <t>GFS</t>
   </si>
@@ -656,56 +656,56 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:O102"/>
+  <dimension ref="A5:P102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="9" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="14" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="10" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="15" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E7" s="2">
         <v>45657</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45291</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44926</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44561</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44196</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43830</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>43465</v>
       </c>
-      <c r="K7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="L7" s="2" t="s">
         <v>3</v>
       </c>
@@ -715,36 +715,39 @@
       <c r="N7" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="O7" s="2"/>
-    </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="O7" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="P7" s="2"/>
+    </row>
+    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>6791000</v>
+      </c>
+      <c r="E8" s="3">
         <v>6750000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>7392000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>8108000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>6585000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>4851000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>5812800</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>6196000</v>
       </c>
-      <c r="K8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L8" s="3" t="s">
         <v>3</v>
       </c>
@@ -754,36 +757,39 @@
       <c r="N8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O8" s="3"/>
-    </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="O8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P8" s="3"/>
+    </row>
+    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>5101000</v>
+      </c>
+      <c r="E9" s="3">
         <v>5099000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>5291000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>5869000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>5572000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>5563000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>6345000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>6646100</v>
       </c>
-      <c r="K9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L9" s="3" t="s">
         <v>3</v>
       </c>
@@ -793,36 +799,39 @@
       <c r="N9" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O9" s="3"/>
-    </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="O9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P9" s="3"/>
+    </row>
+    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>1690000</v>
+      </c>
+      <c r="E10" s="3">
         <v>1651000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>2101000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>2239000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>1013000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>-712000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>-532200</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>-450100</v>
       </c>
-      <c r="K10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L10" s="3" t="s">
         <v>3</v>
       </c>
@@ -832,9 +841,12 @@
       <c r="N10" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O10" s="3"/>
-    </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="O10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P10" s="3"/>
+    </row>
+    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -850,35 +862,36 @@
       <c r="M11" s="3"/>
       <c r="N11" s="3"/>
       <c r="O11" s="3"/>
-    </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P11" s="3"/>
+    </row>
+    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>518000</v>
+      </c>
+      <c r="E12" s="3">
         <v>496000</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>428000</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>482000</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>478000</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>476000</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>583000</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>926200</v>
       </c>
-      <c r="K12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L12" s="3" t="s">
         <v>3</v>
       </c>
@@ -888,9 +901,12 @@
       <c r="N12" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O12" s="3"/>
-    </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="O12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P12" s="3"/>
+    </row>
+    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -927,36 +943,39 @@
       <c r="N13" s="3">
         <v>0</v>
       </c>
-      <c r="O13" s="3"/>
-    </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="O13" s="3">
+        <v>0</v>
+      </c>
+      <c r="P13" s="3"/>
+    </row>
+    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>853000</v>
+        <v>-15000</v>
       </c>
       <c r="E14" s="3">
-        <v>84000</v>
+        <v>942000</v>
       </c>
       <c r="F14" s="3">
+        <v>71000</v>
+      </c>
+      <c r="G14" s="3">
         <v>-412000</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>-39000</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>-449000</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>-624700</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>632900</v>
       </c>
-      <c r="K14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L14" s="3" t="s">
         <v>3</v>
       </c>
@@ -966,38 +985,41 @@
       <c r="N14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O14" s="3"/>
-    </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="O14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P14" s="3"/>
+    </row>
+    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>1251000</v>
+      </c>
+      <c r="E15" s="3">
         <v>1493000</v>
       </c>
-      <c r="E15" s="3">
-        <v>1387000</v>
-      </c>
       <c r="F15" s="3">
+        <v>1451000</v>
+      </c>
+      <c r="G15" s="3">
         <v>1541000</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>1537000</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>2522000</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>2678200</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>2947900</v>
       </c>
-      <c r="K15" s="3">
-        <v>0</v>
-      </c>
-      <c r="L15" s="3" t="s">
-        <v>3</v>
+      <c r="L15" s="3">
+        <v>0</v>
       </c>
       <c r="M15" s="3" t="s">
         <v>3</v>
@@ -1005,9 +1027,12 @@
       <c r="N15" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O15" s="3"/>
-    </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="O15" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P15" s="3"/>
+    </row>
+    <row r="16" spans="1:16" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1020,35 +1045,36 @@
       <c r="M16" s="3"/>
       <c r="N16" s="3"/>
       <c r="O16" s="3"/>
-    </row>
-    <row r="17" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P16" s="3"/>
+    </row>
+    <row r="17" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>5994000</v>
+      </c>
+      <c r="E17" s="3">
         <v>6022000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>6192000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>6847000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>6645000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>6484000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>7373600</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>8025100</v>
       </c>
-      <c r="K17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L17" s="3" t="s">
         <v>3</v>
       </c>
@@ -1058,36 +1084,39 @@
       <c r="N17" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O17" s="3"/>
-    </row>
-    <row r="18" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P17" s="3"/>
+    </row>
+    <row r="18" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>797000</v>
+      </c>
+      <c r="E18" s="3">
         <v>728000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>1200000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>1261000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-60000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-1633000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-1560800</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-1829000</v>
       </c>
-      <c r="K18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1097,9 +1126,12 @@
       <c r="N18" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O18" s="3"/>
-    </row>
-    <row r="19" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P18" s="3"/>
+    </row>
+    <row r="19" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1115,35 +1147,36 @@
       <c r="M19" s="3"/>
       <c r="N19" s="3"/>
       <c r="O19" s="3"/>
-    </row>
-    <row r="20" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P19" s="3"/>
+    </row>
+    <row r="20" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>106000</v>
+        <v>-9000</v>
       </c>
       <c r="E20" s="3">
-        <v>53000</v>
+        <v>17000</v>
       </c>
       <c r="F20" s="3">
+        <v>66000</v>
+      </c>
+      <c r="G20" s="3">
         <v>88000</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>57000</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>51000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>19500</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>20400</v>
       </c>
-      <c r="K20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L20" s="3" t="s">
         <v>3</v>
       </c>
@@ -1153,38 +1186,41 @@
       <c r="N20" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O20" s="3"/>
-    </row>
-    <row r="21" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P20" s="3"/>
+    </row>
+    <row r="21" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>2115000</v>
+        <v>2057000</v>
       </c>
       <c r="E21" s="3">
-        <v>2534000</v>
+        <v>2204000</v>
       </c>
       <c r="F21" s="3">
+        <v>2585000</v>
+      </c>
+      <c r="G21" s="3">
         <v>2714000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>1420000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>838000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>1097800</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>1098500</v>
       </c>
-      <c r="K21" s="3">
-        <v>0</v>
-      </c>
-      <c r="L21" s="3" t="s">
-        <v>3</v>
+      <c r="L21" s="3">
+        <v>0</v>
       </c>
       <c r="M21" s="3" t="s">
         <v>3</v>
@@ -1192,36 +1228,39 @@
       <c r="N21" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O21" s="3"/>
-    </row>
-    <row r="22" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P21" s="3"/>
+    </row>
+    <row r="22" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>50000</v>
+      </c>
+      <c r="E22" s="3">
         <v>106000</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>101000</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>92000</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>99000</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>133000</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>202800</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>137500</v>
       </c>
-      <c r="K22" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L22" s="3" t="s">
         <v>3</v>
       </c>
@@ -1231,36 +1270,39 @@
       <c r="N22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O22" s="3"/>
-    </row>
-    <row r="23" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P22" s="3"/>
+    </row>
+    <row r="23" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>911000</v>
+      </c>
+      <c r="E23" s="3">
         <v>-170000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>1084000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>1532000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-176000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-1365000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-1147100</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-2609600</v>
       </c>
-      <c r="K23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L23" s="3" t="s">
         <v>3</v>
       </c>
@@ -1270,36 +1312,39 @@
       <c r="N23" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O23" s="3"/>
-    </row>
-    <row r="24" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P23" s="3"/>
+    </row>
+    <row r="24" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>23000</v>
+      </c>
+      <c r="E24" s="3">
         <v>92000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>66000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>86000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>78000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>-12000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>224100</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>16400</v>
       </c>
-      <c r="K24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L24" s="3" t="s">
         <v>3</v>
       </c>
@@ -1309,9 +1354,12 @@
       <c r="N24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O24" s="3"/>
-    </row>
-    <row r="25" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P24" s="3"/>
+    </row>
+    <row r="25" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1348,36 +1396,39 @@
       <c r="N25" s="3">
         <v>0</v>
       </c>
-      <c r="O25" s="3"/>
-    </row>
-    <row r="26" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O25" s="3">
+        <v>0</v>
+      </c>
+      <c r="P25" s="3"/>
+    </row>
+    <row r="26" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>888000</v>
+      </c>
+      <c r="E26" s="3">
         <v>-262000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>1018000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>1446000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-254000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-1353000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-1371200</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-2626000</v>
       </c>
-      <c r="K26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L26" s="3" t="s">
         <v>3</v>
       </c>
@@ -1387,36 +1438,39 @@
       <c r="N26" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O26" s="3"/>
-    </row>
-    <row r="27" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P26" s="3"/>
+    </row>
+    <row r="27" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>885000</v>
+      </c>
+      <c r="E27" s="3">
         <v>-265000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>1020000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>1448000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-250000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-1350000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-1371200</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-2701600</v>
       </c>
-      <c r="K27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L27" s="3" t="s">
         <v>3</v>
       </c>
@@ -1426,9 +1480,12 @@
       <c r="N27" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O27" s="3"/>
-    </row>
-    <row r="28" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P27" s="3"/>
+    </row>
+    <row r="28" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1465,9 +1522,12 @@
       <c r="N28" s="3">
         <v>0</v>
       </c>
-      <c r="O28" s="3"/>
-    </row>
-    <row r="29" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O28" s="3">
+        <v>0</v>
+      </c>
+      <c r="P28" s="3"/>
+    </row>
+    <row r="29" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1490,13 +1550,13 @@
         <v>0</v>
       </c>
       <c r="J29" s="3">
+        <v>0</v>
+      </c>
+      <c r="K29" s="3">
         <v>-148000</v>
       </c>
-      <c r="K29" s="3">
-        <v>0</v>
-      </c>
-      <c r="L29" s="3" t="s">
-        <v>3</v>
+      <c r="L29" s="3">
+        <v>0</v>
       </c>
       <c r="M29" s="3" t="s">
         <v>3</v>
@@ -1504,9 +1564,12 @@
       <c r="N29" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O29" s="3"/>
-    </row>
-    <row r="30" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O29" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P29" s="3"/>
+    </row>
+    <row r="30" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1543,9 +1606,12 @@
       <c r="N30" s="3">
         <v>0</v>
       </c>
-      <c r="O30" s="3"/>
-    </row>
-    <row r="31" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O30" s="3">
+        <v>0</v>
+      </c>
+      <c r="P30" s="3"/>
+    </row>
+    <row r="31" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1582,36 +1648,39 @@
       <c r="N31" s="3">
         <v>0</v>
       </c>
-      <c r="O31" s="3"/>
-    </row>
-    <row r="32" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O31" s="3">
+        <v>0</v>
+      </c>
+      <c r="P31" s="3"/>
+    </row>
+    <row r="32" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-106000</v>
+        <v>9000</v>
       </c>
       <c r="E32" s="3">
-        <v>-53000</v>
+        <v>-17000</v>
       </c>
       <c r="F32" s="3">
+        <v>-66000</v>
+      </c>
+      <c r="G32" s="3">
         <v>-88000</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-57000</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-51000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-19500</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-20400</v>
       </c>
-      <c r="K32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L32" s="3" t="s">
         <v>3</v>
       </c>
@@ -1621,36 +1690,39 @@
       <c r="N32" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O32" s="3"/>
-    </row>
-    <row r="33" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P32" s="3"/>
+    </row>
+    <row r="33" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>885000</v>
+      </c>
+      <c r="E33" s="3">
         <v>-265000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>1020000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>1448000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-250000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-1350000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-1371200</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-2701600</v>
       </c>
-      <c r="K33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L33" s="3" t="s">
         <v>3</v>
       </c>
@@ -1660,9 +1732,12 @@
       <c r="N33" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O33" s="3"/>
-    </row>
-    <row r="34" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P33" s="3"/>
+    </row>
+    <row r="34" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1699,36 +1774,39 @@
       <c r="N34" s="3">
         <v>0</v>
       </c>
-      <c r="O34" s="3"/>
-    </row>
-    <row r="35" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O34" s="3">
+        <v>0</v>
+      </c>
+      <c r="P34" s="3"/>
+    </row>
+    <row r="35" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>885000</v>
+      </c>
+      <c r="E35" s="3">
         <v>-265000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>1020000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>1448000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-250000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-1350000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-1371200</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-2701600</v>
       </c>
-      <c r="K35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L35" s="3" t="s">
         <v>3</v>
       </c>
@@ -1738,41 +1816,44 @@
       <c r="N35" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O35" s="3"/>
-    </row>
-    <row r="37" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P35" s="3"/>
+    </row>
+    <row r="37" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E38" s="2">
         <v>45657</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45291</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44926</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44561</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44196</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43830</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>43465</v>
       </c>
-      <c r="K38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="L38" s="2" t="s">
         <v>3</v>
       </c>
@@ -1782,9 +1863,12 @@
       <c r="N38" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="O38" s="2"/>
-    </row>
-    <row r="39" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O38" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="P38" s="2"/>
+    </row>
+    <row r="39" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1800,8 +1884,9 @@
       <c r="M39" s="3"/>
       <c r="N39" s="3"/>
       <c r="O39" s="3"/>
-    </row>
-    <row r="40" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P39" s="3"/>
+    </row>
+    <row r="40" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1817,32 +1902,33 @@
       <c r="M40" s="3"/>
       <c r="N40" s="3"/>
       <c r="O40" s="3"/>
-    </row>
-    <row r="41" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P40" s="3"/>
+    </row>
+    <row r="41" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>1809000</v>
+      </c>
+      <c r="E41" s="3">
         <v>2192000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>2387000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>2352000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>2939000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>908100</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>997300</v>
       </c>
-      <c r="J41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K41" s="3" t="s">
         <v>3</v>
       </c>
@@ -1855,24 +1941,27 @@
       <c r="N41" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O41" s="3"/>
-    </row>
-    <row r="42" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P41" s="3"/>
+    </row>
+    <row r="42" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>1241000</v>
+      </c>
+      <c r="E42" s="3">
         <v>1194000</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>1055000</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>622000</v>
       </c>
-      <c r="G42" s="3">
-        <v>0</v>
-      </c>
       <c r="H42" s="3">
         <v>0</v>
       </c>
@@ -1885,8 +1974,8 @@
       <c r="K42" s="3">
         <v>0</v>
       </c>
-      <c r="L42" s="3" t="s">
-        <v>3</v>
+      <c r="L42" s="3">
+        <v>0</v>
       </c>
       <c r="M42" s="3" t="s">
         <v>3</v>
@@ -1894,33 +1983,36 @@
       <c r="N42" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O42" s="3"/>
-    </row>
-    <row r="43" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O42" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P42" s="3"/>
+    </row>
+    <row r="43" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>1393000</v>
+        <v>1578000</v>
       </c>
       <c r="E43" s="3">
+        <v>1406000</v>
+      </c>
+      <c r="F43" s="3">
         <v>1368000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>1408000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>1208000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>1108600</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>2065400</v>
       </c>
-      <c r="J43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K43" s="3" t="s">
         <v>3</v>
       </c>
@@ -1933,33 +2025,36 @@
       <c r="N43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O43" s="3"/>
-    </row>
-    <row r="44" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P43" s="3"/>
+    </row>
+    <row r="44" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>1577000</v>
+      </c>
+      <c r="E44" s="3">
         <v>1624000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>1487000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>1339000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>1121000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>919500</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>351900</v>
       </c>
-      <c r="J44" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K44" s="3" t="s">
         <v>3</v>
       </c>
@@ -1972,33 +2067,36 @@
       <c r="N44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O44" s="3"/>
-    </row>
-    <row r="45" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P44" s="3"/>
+    </row>
+    <row r="45" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3">
-        <v>13000</v>
-      </c>
-      <c r="E45" s="3">
+      <c r="D45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F45" s="3">
         <v>30000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>79000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>23000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>50500</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>40100</v>
       </c>
-      <c r="J45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K45" s="3" t="s">
         <v>3</v>
       </c>
@@ -2011,33 +2109,36 @@
       <c r="N45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O45" s="3"/>
-    </row>
-    <row r="46" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P45" s="3"/>
+    </row>
+    <row r="46" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>6205000</v>
+      </c>
+      <c r="E46" s="3">
         <v>6416000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>6327000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>5800000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>5291000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>2986700</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>3514200</v>
       </c>
-      <c r="J46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K46" s="3" t="s">
         <v>3</v>
       </c>
@@ -2050,33 +2151,36 @@
       <c r="N46" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O46" s="3"/>
-    </row>
-    <row r="47" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P46" s="3"/>
+    </row>
+    <row r="47" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>890000</v>
+        <v>1148000</v>
       </c>
       <c r="E47" s="3">
+        <v>915000</v>
+      </c>
+      <c r="F47" s="3">
         <v>547000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>416000</v>
       </c>
-      <c r="G47" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H47" s="3">
+      <c r="H47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I47" s="3">
         <v>36700</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>85500</v>
       </c>
-      <c r="J47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K47" s="3" t="s">
         <v>3</v>
       </c>
@@ -2089,33 +2193,36 @@
       <c r="N47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O47" s="3"/>
-    </row>
-    <row r="48" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P47" s="3"/>
+    </row>
+    <row r="48" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>7792000</v>
+      </c>
+      <c r="E48" s="3">
         <v>8260000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>10164000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>10596000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>8713000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>8226200</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>9611300</v>
       </c>
-      <c r="J48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K48" s="3" t="s">
         <v>3</v>
       </c>
@@ -2128,35 +2235,38 @@
       <c r="N48" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O48" s="3"/>
-    </row>
-    <row r="49" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P48" s="3"/>
+    </row>
+    <row r="49" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>1368000</v>
+      </c>
+      <c r="E49" s="3">
         <v>660000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>391000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>363000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>377000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>547900</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>634800</v>
       </c>
-      <c r="J49" s="3">
-        <v>0</v>
-      </c>
-      <c r="K49" s="3" t="s">
-        <v>3</v>
+      <c r="K49" s="3">
+        <v>0</v>
       </c>
       <c r="L49" s="3" t="s">
         <v>3</v>
@@ -2167,9 +2277,12 @@
       <c r="N49" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O49" s="3"/>
-    </row>
-    <row r="50" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O49" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P49" s="3"/>
+    </row>
+    <row r="50" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2206,9 +2319,12 @@
       <c r="N50" s="3">
         <v>0</v>
       </c>
-      <c r="O50" s="3"/>
-    </row>
-    <row r="51" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O50" s="3">
+        <v>0</v>
+      </c>
+      <c r="P50" s="3"/>
+    </row>
+    <row r="51" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2245,33 +2361,36 @@
       <c r="N51" s="3">
         <v>0</v>
       </c>
-      <c r="O51" s="3"/>
-    </row>
-    <row r="52" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O51" s="3">
+        <v>0</v>
+      </c>
+      <c r="P51" s="3"/>
+    </row>
+    <row r="52" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>385000</v>
+        <v>379000</v>
       </c>
       <c r="E52" s="3">
-        <v>374000</v>
+        <v>360000</v>
       </c>
       <c r="F52" s="3">
         <v>374000</v>
       </c>
       <c r="G52" s="3">
+        <v>374000</v>
+      </c>
+      <c r="H52" s="3">
         <v>294000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>80500</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>118200</v>
       </c>
-      <c r="J52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K52" s="3" t="s">
         <v>3</v>
       </c>
@@ -2284,9 +2403,12 @@
       <c r="N52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O52" s="3"/>
-    </row>
-    <row r="53" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P52" s="3"/>
+    </row>
+    <row r="53" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2323,33 +2445,36 @@
       <c r="N53" s="3">
         <v>0</v>
       </c>
-      <c r="O53" s="3"/>
-    </row>
-    <row r="54" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O53" s="3">
+        <v>0</v>
+      </c>
+      <c r="P53" s="3"/>
+    </row>
+    <row r="54" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>17141000</v>
+      </c>
+      <c r="E54" s="3">
         <v>16799000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>18044000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>17841000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>15028000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>12321600</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>14497500</v>
       </c>
-      <c r="J54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K54" s="3" t="s">
         <v>3</v>
       </c>
@@ -2362,9 +2487,12 @@
       <c r="N54" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O54" s="3"/>
-    </row>
-    <row r="55" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P54" s="3"/>
+    </row>
+    <row r="55" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2380,8 +2508,9 @@
       <c r="M55" s="3"/>
       <c r="N55" s="3"/>
       <c r="O55" s="3"/>
-    </row>
-    <row r="56" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P55" s="3"/>
+    </row>
+    <row r="56" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2397,32 +2526,33 @@
       <c r="M56" s="3"/>
       <c r="N56" s="3"/>
       <c r="O56" s="3"/>
-    </row>
-    <row r="57" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P56" s="3"/>
+    </row>
+    <row r="57" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>491000</v>
+      </c>
+      <c r="E57" s="3">
         <v>406000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>511000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>532000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>551000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>414500</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>4000</v>
       </c>
-      <c r="J57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K57" s="3" t="s">
         <v>3</v>
       </c>
@@ -2435,35 +2565,38 @@
       <c r="N57" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O57" s="3"/>
-    </row>
-    <row r="58" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P57" s="3"/>
+    </row>
+    <row r="58" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>155000</v>
+      </c>
+      <c r="E58" s="3">
         <v>843000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>606000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>298000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>432000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>513100</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>817800</v>
       </c>
-      <c r="J58" s="3">
-        <v>0</v>
-      </c>
-      <c r="K58" s="3" t="s">
-        <v>3</v>
+      <c r="K58" s="3">
+        <v>0</v>
       </c>
       <c r="L58" s="3" t="s">
         <v>3</v>
@@ -2474,33 +2607,36 @@
       <c r="N58" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O58" s="3"/>
-    </row>
-    <row r="59" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P58" s="3"/>
+    </row>
+    <row r="59" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>1270000</v>
+      </c>
+      <c r="E59" s="3">
         <v>1273000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>1486000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>1956000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>1577000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>497600</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>955400</v>
       </c>
-      <c r="J59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K59" s="3" t="s">
         <v>3</v>
       </c>
@@ -2513,33 +2649,36 @@
       <c r="N59" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O59" s="3"/>
-    </row>
-    <row r="60" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P59" s="3"/>
+    </row>
+    <row r="60" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>2368000</v>
+      </c>
+      <c r="E60" s="3">
         <v>3044000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>3099000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>3359000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>3163000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>1896100</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>2336100</v>
       </c>
-      <c r="J60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K60" s="3" t="s">
         <v>3</v>
       </c>
@@ -2552,33 +2691,36 @@
       <c r="N60" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O60" s="3"/>
-    </row>
-    <row r="61" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P60" s="3"/>
+    </row>
+    <row r="61" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>1552000</v>
+      </c>
+      <c r="E61" s="3">
         <v>1478000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>2151000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>2561000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>2015000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>2322700</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>2430500</v>
       </c>
-      <c r="J61" s="3">
-        <v>0</v>
-      </c>
       <c r="K61" s="3">
         <v>0</v>
       </c>
@@ -2591,33 +2733,36 @@
       <c r="N61" s="3">
         <v>0</v>
       </c>
-      <c r="O61" s="3"/>
-    </row>
-    <row r="62" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O61" s="3">
+        <v>0</v>
+      </c>
+      <c r="P61" s="3"/>
+    </row>
+    <row r="62" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>408000</v>
+      </c>
+      <c r="E62" s="3">
         <v>449000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>282000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>315000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>300000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>694000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>515100</v>
       </c>
-      <c r="J62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K62" s="3" t="s">
         <v>3</v>
       </c>
@@ -2630,9 +2775,12 @@
       <c r="N62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O62" s="3"/>
-    </row>
-    <row r="63" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P62" s="3"/>
+    </row>
+    <row r="63" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2669,9 +2817,12 @@
       <c r="N63" s="3">
         <v>0</v>
       </c>
-      <c r="O63" s="3"/>
-    </row>
-    <row r="64" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O63" s="3">
+        <v>0</v>
+      </c>
+      <c r="P63" s="3"/>
+    </row>
+    <row r="64" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2708,9 +2859,12 @@
       <c r="N64" s="3">
         <v>0</v>
       </c>
-      <c r="O64" s="3"/>
-    </row>
-    <row r="65" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O64" s="3">
+        <v>0</v>
+      </c>
+      <c r="P64" s="3"/>
+    </row>
+    <row r="65" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2747,33 +2901,36 @@
       <c r="N65" s="3">
         <v>0</v>
       </c>
-      <c r="O65" s="3"/>
-    </row>
-    <row r="66" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O65" s="3">
+        <v>0</v>
+      </c>
+      <c r="P65" s="3"/>
+    </row>
+    <row r="66" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>5158000</v>
+      </c>
+      <c r="E66" s="3">
         <v>5975000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>6893000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>7881000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>6995000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>5080100</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>5478400</v>
       </c>
-      <c r="J66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K66" s="3" t="s">
         <v>3</v>
       </c>
@@ -2786,9 +2943,12 @@
       <c r="N66" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O66" s="3"/>
-    </row>
-    <row r="67" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P66" s="3"/>
+    </row>
+    <row r="67" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2804,8 +2964,9 @@
       <c r="M67" s="3"/>
       <c r="N67" s="3"/>
       <c r="O67" s="3"/>
-    </row>
-    <row r="68" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P67" s="3"/>
+    </row>
+    <row r="68" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2842,9 +3003,12 @@
       <c r="N68" s="3">
         <v>0</v>
       </c>
-      <c r="O68" s="3"/>
-    </row>
-    <row r="69" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O68" s="3">
+        <v>0</v>
+      </c>
+      <c r="P68" s="3"/>
+    </row>
+    <row r="69" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2881,9 +3045,12 @@
       <c r="N69" s="3">
         <v>0</v>
       </c>
-      <c r="O69" s="3"/>
-    </row>
-    <row r="70" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O69" s="3">
+        <v>0</v>
+      </c>
+      <c r="P69" s="3"/>
+    </row>
+    <row r="70" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -2920,9 +3087,12 @@
       <c r="N70" s="3">
         <v>0</v>
       </c>
-      <c r="O70" s="3"/>
-    </row>
-    <row r="71" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O70" s="3">
+        <v>0</v>
+      </c>
+      <c r="P70" s="3"/>
+    </row>
+    <row r="71" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -2959,33 +3129,36 @@
       <c r="N71" s="3">
         <v>0</v>
       </c>
-      <c r="O71" s="3"/>
-    </row>
-    <row r="72" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O71" s="3">
+        <v>0</v>
+      </c>
+      <c r="P71" s="3"/>
+    </row>
+    <row r="72" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-12381000</v>
+      </c>
+      <c r="E72" s="3">
         <v>-13266000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-13001000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-14021000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-15469000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-15218500</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-13870900</v>
       </c>
-      <c r="J72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K72" s="3" t="s">
         <v>3</v>
       </c>
@@ -2998,9 +3171,12 @@
       <c r="N72" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O72" s="3"/>
-    </row>
-    <row r="73" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P72" s="3"/>
+    </row>
+    <row r="73" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3037,9 +3213,12 @@
       <c r="N73" s="3">
         <v>0</v>
       </c>
-      <c r="O73" s="3"/>
-    </row>
-    <row r="74" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O73" s="3">
+        <v>0</v>
+      </c>
+      <c r="P73" s="3"/>
+    </row>
+    <row r="74" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3076,9 +3255,12 @@
       <c r="N74" s="3">
         <v>0</v>
       </c>
-      <c r="O74" s="3"/>
-    </row>
-    <row r="75" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O74" s="3">
+        <v>0</v>
+      </c>
+      <c r="P74" s="3"/>
+    </row>
+    <row r="75" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3115,33 +3297,36 @@
       <c r="N75" s="3">
         <v>0</v>
       </c>
-      <c r="O75" s="3"/>
-    </row>
-    <row r="76" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O75" s="3">
+        <v>0</v>
+      </c>
+      <c r="P75" s="3"/>
+    </row>
+    <row r="76" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>11928000</v>
+      </c>
+      <c r="E76" s="3">
         <v>10776000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>11104000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>9913000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>7975000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>7176400</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>9019100</v>
       </c>
-      <c r="J76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K76" s="3" t="s">
         <v>3</v>
       </c>
@@ -3154,9 +3339,12 @@
       <c r="N76" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O76" s="3"/>
-    </row>
-    <row r="77" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P76" s="3"/>
+    </row>
+    <row r="77" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3193,41 +3381,44 @@
       <c r="N77" s="3">
         <v>0</v>
       </c>
-      <c r="O77" s="3"/>
-    </row>
-    <row r="79" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O77" s="3">
+        <v>0</v>
+      </c>
+      <c r="P77" s="3"/>
+    </row>
+    <row r="79" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E80" s="2">
         <v>45657</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45291</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44926</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44561</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44196</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43830</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>43465</v>
       </c>
-      <c r="K80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="L80" s="2" t="s">
         <v>3</v>
       </c>
@@ -3237,36 +3428,39 @@
       <c r="N80" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="O80" s="2"/>
-    </row>
-    <row r="81" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O80" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="P80" s="2"/>
+    </row>
+    <row r="81" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>885000</v>
+      </c>
+      <c r="E81" s="3">
         <v>-265000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>1020000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>1448000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-250000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-1350000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-1371200</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-2701600</v>
       </c>
-      <c r="K81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L81" s="3" t="s">
         <v>3</v>
       </c>
@@ -3276,9 +3470,12 @@
       <c r="N81" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O81" s="3"/>
-    </row>
-    <row r="82" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P81" s="3"/>
+    </row>
+    <row r="82" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3294,35 +3491,36 @@
       <c r="M82" s="3"/>
       <c r="N82" s="3"/>
       <c r="O82" s="3"/>
-    </row>
-    <row r="83" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P82" s="3"/>
+    </row>
+    <row r="83" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>1185000</v>
+      </c>
+      <c r="E83" s="3">
         <v>1442000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>1322000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>1447000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>1411000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>2238000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>2435900</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>2683200</v>
       </c>
-      <c r="K83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L83" s="3" t="s">
         <v>3</v>
       </c>
@@ -3332,9 +3530,12 @@
       <c r="N83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O83" s="3"/>
-    </row>
-    <row r="84" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P83" s="3"/>
+    </row>
+    <row r="84" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3371,9 +3572,12 @@
       <c r="N84" s="3">
         <v>0</v>
       </c>
-      <c r="O84" s="3"/>
-    </row>
-    <row r="85" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O84" s="3">
+        <v>0</v>
+      </c>
+      <c r="P84" s="3"/>
+    </row>
+    <row r="85" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3410,9 +3614,12 @@
       <c r="N85" s="3">
         <v>0</v>
       </c>
-      <c r="O85" s="3"/>
-    </row>
-    <row r="86" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O85" s="3">
+        <v>0</v>
+      </c>
+      <c r="P85" s="3"/>
+    </row>
+    <row r="86" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3449,9 +3656,12 @@
       <c r="N86" s="3">
         <v>0</v>
       </c>
-      <c r="O86" s="3"/>
-    </row>
-    <row r="87" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O86" s="3">
+        <v>0</v>
+      </c>
+      <c r="P86" s="3"/>
+    </row>
+    <row r="87" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3488,9 +3698,12 @@
       <c r="N87" s="3">
         <v>0</v>
       </c>
-      <c r="O87" s="3"/>
-    </row>
-    <row r="88" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O87" s="3">
+        <v>0</v>
+      </c>
+      <c r="P87" s="3"/>
+    </row>
+    <row r="88" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3527,36 +3740,39 @@
       <c r="N88" s="3">
         <v>0</v>
       </c>
-      <c r="O88" s="3"/>
-    </row>
-    <row r="89" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O88" s="3">
+        <v>0</v>
+      </c>
+      <c r="P88" s="3"/>
+    </row>
+    <row r="89" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>1731000</v>
+      </c>
+      <c r="E89" s="3">
         <v>1722000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>2125000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>2624000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>2839000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>1004000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>496800</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>279300</v>
       </c>
-      <c r="K89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L89" s="3" t="s">
         <v>3</v>
       </c>
@@ -3566,9 +3782,12 @@
       <c r="N89" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O89" s="3"/>
-    </row>
-    <row r="90" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P89" s="3"/>
+    </row>
+    <row r="90" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3584,35 +3803,36 @@
       <c r="M90" s="3"/>
       <c r="N90" s="3"/>
       <c r="O90" s="3"/>
-    </row>
-    <row r="91" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P90" s="3"/>
+    </row>
+    <row r="91" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-722000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-625000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-1804000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-3059000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-1767000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-592000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-587900</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-1150300</v>
       </c>
-      <c r="K91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L91" s="3" t="s">
         <v>3</v>
       </c>
@@ -3622,9 +3842,12 @@
       <c r="N91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O91" s="3"/>
-    </row>
-    <row r="92" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P91" s="3"/>
+    </row>
+    <row r="92" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3661,9 +3884,12 @@
       <c r="N92" s="3">
         <v>0</v>
       </c>
-      <c r="O92" s="3"/>
-    </row>
-    <row r="93" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O92" s="3">
+        <v>0</v>
+      </c>
+      <c r="P92" s="3"/>
+    </row>
+    <row r="93" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3700,36 +3926,39 @@
       <c r="N93" s="3">
         <v>0</v>
       </c>
-      <c r="O93" s="3"/>
-    </row>
-    <row r="94" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O93" s="3">
+        <v>0</v>
+      </c>
+      <c r="P93" s="3"/>
+    </row>
+    <row r="94" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-1274000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-1125000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-1882000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-4058000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-1450000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-366000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>343700</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-1167200</v>
       </c>
-      <c r="K94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L94" s="3" t="s">
         <v>3</v>
       </c>
@@ -3739,9 +3968,12 @@
       <c r="N94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O94" s="3"/>
-    </row>
-    <row r="95" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P94" s="3"/>
+    </row>
+    <row r="95" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3757,8 +3989,9 @@
       <c r="M95" s="3"/>
       <c r="N95" s="3"/>
       <c r="O95" s="3"/>
-    </row>
-    <row r="96" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P95" s="3"/>
+    </row>
+    <row r="96" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -3795,9 +4028,12 @@
       <c r="N96" s="3">
         <v>0</v>
       </c>
-      <c r="O96" s="3"/>
-    </row>
-    <row r="97" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O96" s="3">
+        <v>0</v>
+      </c>
+      <c r="P96" s="3"/>
+    </row>
+    <row r="97" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3834,9 +4070,12 @@
       <c r="N97" s="3">
         <v>0</v>
       </c>
-      <c r="O97" s="3"/>
-    </row>
-    <row r="98" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O97" s="3">
+        <v>0</v>
+      </c>
+      <c r="P97" s="3"/>
+    </row>
+    <row r="98" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -3873,9 +4112,12 @@
       <c r="N98" s="3">
         <v>0</v>
       </c>
-      <c r="O98" s="3"/>
-    </row>
-    <row r="99" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O98" s="3">
+        <v>0</v>
+      </c>
+      <c r="P98" s="3"/>
+    </row>
+    <row r="99" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -3912,36 +4154,39 @@
       <c r="N99" s="3">
         <v>0</v>
       </c>
-      <c r="O99" s="3"/>
-    </row>
-    <row r="100" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O99" s="3">
+        <v>0</v>
+      </c>
+      <c r="P99" s="3"/>
+    </row>
+    <row r="100" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-845000</v>
+      </c>
+      <c r="E100" s="3">
         <v>-785000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-212000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>842000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>650000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-733000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-683800</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>1132100</v>
       </c>
-      <c r="K100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L100" s="3" t="s">
         <v>3</v>
       </c>
@@ -3951,36 +4196,39 @@
       <c r="N100" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O100" s="3"/>
-    </row>
-    <row r="101" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P100" s="3"/>
+    </row>
+    <row r="101" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>5000</v>
+      </c>
+      <c r="E101" s="3">
         <v>-7000</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>4000</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>5000</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-8000</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>6000</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-3400</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-1300</v>
       </c>
-      <c r="K101" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L101" s="3" t="s">
         <v>3</v>
       </c>
@@ -3990,38 +4238,41 @@
       <c r="N101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O101" s="3"/>
-    </row>
-    <row r="102" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P101" s="3"/>
+    </row>
+    <row r="102" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-383000</v>
+      </c>
+      <c r="E102" s="3">
         <v>-195000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>35000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-587000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>2031000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-89000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>153300</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>242900</v>
       </c>
-      <c r="K102" s="3">
-        <v>0</v>
-      </c>
-      <c r="L102" s="3" t="s">
-        <v>3</v>
+      <c r="L102" s="3">
+        <v>0</v>
       </c>
       <c r="M102" s="3" t="s">
         <v>3</v>
@@ -4029,7 +4280,10 @@
       <c r="N102" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O102" s="3"/>
+      <c r="O102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/AAII_Financials/Yearly/GFS_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/GFS_YR_FIN.xlsx
@@ -953,7 +953,7 @@
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>-15000</v>
+        <v>-46000</v>
       </c>
       <c r="E14" s="3">
         <v>942000</v>
@@ -1154,7 +1154,7 @@
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>-9000</v>
+        <v>22000</v>
       </c>
       <c r="E20" s="3">
         <v>17000</v>
@@ -1196,7 +1196,7 @@
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>2057000</v>
+        <v>2026000</v>
       </c>
       <c r="E21" s="3">
         <v>2204000</v>
@@ -1658,7 +1658,7 @@
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>9000</v>
+        <v>-22000</v>
       </c>
       <c r="E32" s="3">
         <v>-17000</v>
